--- a/★정리★/4_감성 사전/sentiment_dict.xlsx
+++ b/★정리★/4_감성 사전/sentiment_dict.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\reply\Desktop\2026-1\수업_데이터마이닝\Project\★정리★\4_감성 사전\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F1553981-9802-4903-96EB-2D06ECC778E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E000F7DC-BF91-42D7-AAC0-A42E57CE906D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17430" yWindow="0" windowWidth="8260" windowHeight="15370" xr2:uid="{B8F84E31-54CE-4C13-8E19-FE22CE9ABC30}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{B8F84E31-54CE-4C13-8E19-FE22CE9ABC30}"/>
   </bookViews>
   <sheets>
     <sheet name="sentiment_dict" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="212">
   <si>
     <t>word</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -258,10 +258,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>푸짐*푸다 짐함 으로 분리됨</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>번창</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -282,10 +278,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>맥락이 중요한 단어(눈치 등)는 일단 제외</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>달짝지근하다</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -326,7 +318,555 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>category(naver)</t>
+    <t>건강하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>감사</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>불쾌하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>안되다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그냥</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>당황</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>급하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>느끼하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>모호</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>더럽다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>색다르다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>비법</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>굿굿</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>양도</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>끝내주다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>길다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>싱싱하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>얼큰하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>달콤하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>곁들이다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>당기다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>눈물나다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>충분하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>충만</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>조용하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>촉촉하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>단점</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>질도</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>어렵다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>심하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>보드랍다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>미치다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>다양하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>만족스럽다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>감탄</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>편하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>추천</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>빠르다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>시큰둥하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>최악</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>소진</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아깝다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>던지다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>별로</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>다만</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>근데</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>무척</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>매우</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>훌륭하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>대기+많다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>대기+길다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>정갈하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>인상+깊다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>짜다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>퍽퍽</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>않다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>어울리다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>보람</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>야무지다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>여전하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>덥다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>담백하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>벌레</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>즐겁다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>쫀든쫀든한</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>지저분하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>행주</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>시끄럽다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>착하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>맛집</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>북적</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>활기</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>인생</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>조만간</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>정신</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>압도</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>저렴하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>행복</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>쓴소리</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>질리다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>미안하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>적다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>존맛</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>대박나다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>감사하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>거절</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>신고</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>부족하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>낄낄대다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>공산주의</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>잡치다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>고성방가</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>개존맛</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>협소</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>개굿</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>굿</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>크다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>에바</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>뜨끈하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>금방</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>쵹쵹</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>끈적</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>딱이다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>혼잡</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>삿대질</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>파리</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿰쿰하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>비리다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>답답하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>배탈</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>독촉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>뉘앙스</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>심각하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>부실하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>달다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>특색</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>싸가지</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>바퀴벌레</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>애매하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>의문</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>내공</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>흐물흐물</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>차갑다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>질김</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>질기다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>추억</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>개판</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>태도</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>어이없다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>부적합</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>시원하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>딱좋다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>두툼하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>깨끗하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>충실하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>미지근하다</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>인사+안함</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>쫀득쫀득한</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -495,7 +1035,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -673,6 +1213,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -920,7 +1472,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -932,6 +1484,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -980,6 +1544,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFF99"/>
+      <color rgb="FFFFFFCC"/>
+      <color rgb="FFFFFF00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1308,33 +1879,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B34153-A18F-4594-BFBD-B7DABCC152FE}">
-  <dimension ref="A1:Q4269"/>
+  <dimension ref="A2:T4270"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,42 +1907,48 @@
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+    </row>
+    <row r="3" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="6"/>
+      <c r="I3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
+      <c r="J3" s="6"/>
+      <c r="K3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3" t="s">
+      <c r="L3" s="6"/>
+      <c r="M3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3" t="s">
+      <c r="N3" s="6"/>
+      <c r="O3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="3"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1444,10 +1998,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>13</v>
       </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
       <c r="C5" t="s">
         <v>2</v>
       </c>
@@ -1463,13 +2020,22 @@
       <c r="K5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="M5" t="s">
+        <v>98</v>
+      </c>
+      <c r="O5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
         <v>42</v>
@@ -1480,13 +2046,25 @@
       <c r="K6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="M6" t="s">
+        <v>131</v>
+      </c>
+      <c r="O6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>17</v>
       </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>81</v>
+      </c>
       <c r="E7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I7" t="s">
         <v>24</v>
@@ -1494,13 +2072,25 @@
       <c r="K7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="M7" t="s">
+        <v>137</v>
+      </c>
+      <c r="O7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>21</v>
       </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
       <c r="E8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I8" t="s">
         <v>8</v>
@@ -1508,287 +2098,931 @@
       <c r="K8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="M8" t="s">
+        <v>145</v>
+      </c>
+      <c r="O8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>22</v>
       </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" t="s">
+        <v>142</v>
+      </c>
       <c r="I9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="M9" t="s">
+        <v>151</v>
+      </c>
+      <c r="O9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>23</v>
       </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E10" t="s">
+        <v>150</v>
+      </c>
       <c r="I10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="M10" t="s">
+        <v>173</v>
+      </c>
+      <c r="O10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>25</v>
       </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>127</v>
+      </c>
       <c r="I11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="M11" t="s">
+        <v>199</v>
+      </c>
+      <c r="O11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>27</v>
       </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>128</v>
+      </c>
+      <c r="I12" t="s">
+        <v>75</v>
+      </c>
       <c r="K12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="M12" t="s">
+        <v>205</v>
+      </c>
+      <c r="O12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>28</v>
       </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I13" t="s">
+        <v>72</v>
+      </c>
       <c r="K13" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="M13" t="s">
+        <v>207</v>
+      </c>
+      <c r="O13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>29</v>
       </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>155</v>
+      </c>
+      <c r="I14" t="s">
+        <v>147</v>
+      </c>
       <c r="K14" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="O14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>30</v>
       </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" t="s">
+        <v>157</v>
+      </c>
       <c r="K15" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="O15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>38</v>
       </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>161</v>
+      </c>
+      <c r="I16" t="s">
+        <v>158</v>
+      </c>
       <c r="K16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.45">
+        <v>103</v>
+      </c>
+      <c r="O16" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>39</v>
       </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>180</v>
+      </c>
       <c r="K17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O17" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>41</v>
       </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>181</v>
+      </c>
       <c r="K18" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O18" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>44</v>
       </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
+      <c r="C19" t="s">
+        <v>183</v>
+      </c>
       <c r="K19" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>107</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
+        <v>186</v>
       </c>
       <c r="K20" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O20" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>58</v>
       </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>187</v>
+      </c>
       <c r="K21" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O21" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>60</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>188</v>
       </c>
       <c r="K22" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O22" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>192</v>
       </c>
       <c r="K23" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>193</v>
       </c>
       <c r="K24" t="s">
         <v>49</v>
       </c>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>195</v>
       </c>
       <c r="K25" t="s">
         <v>50</v>
       </c>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>66</v>
+        <v>64</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>196</v>
       </c>
       <c r="K26" t="s">
         <v>51</v>
       </c>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>65</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>197</v>
       </c>
       <c r="K27" t="s">
         <v>52</v>
       </c>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>69</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28" t="s">
+        <v>198</v>
       </c>
       <c r="K28" t="s">
         <v>53</v>
       </c>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>70</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>209</v>
       </c>
       <c r="K29" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>153</v>
       </c>
       <c r="K30" t="s">
         <v>55</v>
       </c>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
       <c r="K31" t="s">
         <v>56</v>
       </c>
       <c r="N31" s="1"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
       <c r="K32" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N36" s="1"/>
-    </row>
-    <row r="37" spans="14:14" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33">
+        <v>2</v>
+      </c>
+      <c r="K33" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="K34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="K35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="K36" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="K37" t="s">
+        <v>78</v>
+      </c>
       <c r="N37" s="1"/>
     </row>
-    <row r="40" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N40" s="1"/>
-    </row>
-    <row r="47" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N47" s="1"/>
-    </row>
-    <row r="48" spans="14:14" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="K38" t="s">
+        <v>79</v>
+      </c>
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="K39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40">
+        <v>2</v>
+      </c>
+      <c r="K40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="K41" t="s">
+        <v>112</v>
+      </c>
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>94</v>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="K43" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
+      </c>
+      <c r="K44" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="K45" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="K46" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="K47" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>104</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="K48" t="s">
+        <v>140</v>
+      </c>
       <c r="N48" s="1"/>
     </row>
-    <row r="52" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N52" s="1"/>
-    </row>
-    <row r="55" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N55" s="1"/>
-    </row>
-    <row r="59" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N59" s="1"/>
-    </row>
-    <row r="62" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N62" s="1"/>
-    </row>
-    <row r="64" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N64" s="1"/>
-    </row>
-    <row r="66" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N66" s="1"/>
-    </row>
-    <row r="70" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N70" s="1"/>
-    </row>
-    <row r="72" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N72" s="1"/>
-    </row>
-    <row r="74" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N74" s="1"/>
-    </row>
-    <row r="80" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N80" s="1"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N82" s="1"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N85" s="1"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N87" s="1"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="C89" s="1"/>
-      <c r="N89" s="1"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49">
+        <v>2</v>
+      </c>
+      <c r="K49" t="s">
+        <v>152</v>
+      </c>
+      <c r="N49" s="1"/>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="K50" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51">
+        <v>3</v>
+      </c>
+      <c r="K51" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>109</v>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="K52" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>110</v>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="K53" t="s">
+        <v>162</v>
+      </c>
+      <c r="N53" s="1"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>111</v>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="K54" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="K55" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="K56" t="s">
+        <v>171</v>
+      </c>
+      <c r="N56" s="1"/>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>122</v>
+      </c>
+      <c r="B57">
+        <v>3</v>
+      </c>
+      <c r="K57" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>125</v>
+      </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+      <c r="K58" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>126</v>
+      </c>
+      <c r="K59" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>130</v>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="K60" t="s">
+        <v>43</v>
+      </c>
+      <c r="N60" s="1"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>132</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="K61" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="K62" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>135</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="K63" t="s">
+        <v>201</v>
+      </c>
+      <c r="N63" s="1"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>211</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="K64" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A65" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="K65" t="s">
+        <v>210</v>
+      </c>
+      <c r="N65" s="1"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A67" t="s">
+        <v>146</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="N67" s="1"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A68" t="s">
+        <v>149</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A70" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A71" t="s">
+        <v>166</v>
+      </c>
+      <c r="N71" s="1"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A72" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A73" t="s">
+        <v>169</v>
+      </c>
+      <c r="N73" s="1"/>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A74" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A75" t="s">
+        <v>172</v>
+      </c>
+      <c r="N75" s="1"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A76" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A77" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A78" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A79" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A80" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A81" t="s">
+        <v>206</v>
+      </c>
+      <c r="N81" s="1"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A82" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="N83" s="1"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="N86" s="1"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="N88" s="1"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C90" s="1"/>
       <c r="N90" s="1"/>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N95" s="1"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N98" s="1"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N102" s="1"/>
-    </row>
-    <row r="104" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="C104" s="1"/>
-    </row>
-    <row r="107" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N107" s="1"/>
-    </row>
-    <row r="113" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N113" s="1"/>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="N91" s="1"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="N96" s="1"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N99" s="1"/>
+    </row>
+    <row r="103" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N103" s="1"/>
+    </row>
+    <row r="105" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C105" s="1"/>
+    </row>
+    <row r="108" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N108" s="1"/>
     </row>
     <row r="114" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N114" s="1"/>
@@ -1796,80 +3030,80 @@
     <row r="115" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N115" s="1"/>
     </row>
-    <row r="119" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N119" s="1"/>
-    </row>
-    <row r="130" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N130" s="1"/>
-    </row>
-    <row r="141" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N141" s="1"/>
-    </row>
-    <row r="145" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N145" s="1"/>
-    </row>
-    <row r="147" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N147" s="1"/>
-    </row>
-    <row r="149" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N149" s="1"/>
-    </row>
-    <row r="154" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N154" s="1"/>
+    <row r="116" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N116" s="1"/>
+    </row>
+    <row r="120" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N120" s="1"/>
+    </row>
+    <row r="131" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N131" s="1"/>
+    </row>
+    <row r="142" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N142" s="1"/>
+    </row>
+    <row r="146" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N146" s="1"/>
+    </row>
+    <row r="148" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N148" s="1"/>
+    </row>
+    <row r="150" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N150" s="1"/>
     </row>
     <row r="155" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N155" s="1"/>
     </row>
-    <row r="158" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N158" s="1"/>
+    <row r="156" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N156" s="1"/>
     </row>
     <row r="159" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N159" s="1"/>
     </row>
-    <row r="163" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N163" s="1"/>
+    <row r="160" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N160" s="1"/>
     </row>
     <row r="164" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N164" s="1"/>
     </row>
-    <row r="171" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N171" s="1"/>
-    </row>
-    <row r="175" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N175" s="1"/>
-    </row>
-    <row r="180" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N180" s="1"/>
-    </row>
-    <row r="190" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N190" s="1"/>
+    <row r="165" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N165" s="1"/>
+    </row>
+    <row r="172" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N172" s="1"/>
+    </row>
+    <row r="176" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N176" s="1"/>
+    </row>
+    <row r="181" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N181" s="1"/>
     </row>
     <row r="191" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N191" s="1"/>
     </row>
-    <row r="197" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N197" s="1"/>
-    </row>
-    <row r="199" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N199" s="1"/>
-    </row>
-    <row r="202" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N202" s="1"/>
-    </row>
-    <row r="207" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N207" s="1"/>
-    </row>
-    <row r="209" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N209" s="1"/>
-    </row>
-    <row r="213" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N213" s="1"/>
-    </row>
-    <row r="215" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N215" s="1"/>
-    </row>
-    <row r="220" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N220" s="1"/>
+    <row r="192" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N192" s="1"/>
+    </row>
+    <row r="198" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N198" s="1"/>
+    </row>
+    <row r="200" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N200" s="1"/>
+    </row>
+    <row r="203" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N203" s="1"/>
+    </row>
+    <row r="208" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N208" s="1"/>
+    </row>
+    <row r="210" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N210" s="1"/>
+    </row>
+    <row r="214" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N214" s="1"/>
+    </row>
+    <row r="216" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N216" s="1"/>
     </row>
     <row r="221" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N221" s="1"/>
@@ -1880,26 +3114,26 @@
     <row r="223" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N223" s="1"/>
     </row>
-    <row r="228" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N228" s="1"/>
-    </row>
-    <row r="230" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N230" s="1"/>
+    <row r="224" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N224" s="1"/>
+    </row>
+    <row r="229" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N229" s="1"/>
     </row>
     <row r="231" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N231" s="1"/>
     </row>
-    <row r="254" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N254" s="1"/>
-    </row>
-    <row r="263" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N263" s="1"/>
+    <row r="232" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N232" s="1"/>
+    </row>
+    <row r="255" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N255" s="1"/>
     </row>
     <row r="264" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N264" s="1"/>
     </row>
-    <row r="267" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N267" s="1"/>
+    <row r="265" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N265" s="1"/>
     </row>
     <row r="268" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N268" s="1"/>
@@ -1907,104 +3141,104 @@
     <row r="269" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N269" s="1"/>
     </row>
-    <row r="275" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N275" s="1"/>
-    </row>
-    <row r="284" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N284" s="1"/>
+    <row r="270" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N270" s="1"/>
+    </row>
+    <row r="276" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N276" s="1"/>
     </row>
     <row r="285" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N285" s="1"/>
     </row>
-    <row r="288" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N288" s="1"/>
-    </row>
-    <row r="290" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N290" s="1"/>
-    </row>
-    <row r="297" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N297" s="1"/>
+    <row r="286" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N286" s="1"/>
+    </row>
+    <row r="289" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N289" s="1"/>
+    </row>
+    <row r="291" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N291" s="1"/>
     </row>
     <row r="298" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N298" s="1"/>
     </row>
-    <row r="303" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N303" s="1"/>
+    <row r="299" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N299" s="1"/>
     </row>
     <row r="304" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N304" s="1"/>
     </row>
-    <row r="309" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N309" s="1"/>
-    </row>
-    <row r="311" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N311" s="1"/>
-    </row>
-    <row r="315" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N315" s="1"/>
-    </row>
-    <row r="318" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N318" s="1"/>
-    </row>
-    <row r="328" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N328" s="1"/>
-    </row>
-    <row r="330" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N330" s="1"/>
-    </row>
-    <row r="333" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N333" s="1"/>
+    <row r="305" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N305" s="1"/>
+    </row>
+    <row r="310" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N310" s="1"/>
+    </row>
+    <row r="312" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N312" s="1"/>
+    </row>
+    <row r="316" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N316" s="1"/>
+    </row>
+    <row r="319" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N319" s="1"/>
+    </row>
+    <row r="329" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N329" s="1"/>
+    </row>
+    <row r="331" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N331" s="1"/>
     </row>
     <row r="334" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N334" s="1"/>
     </row>
-    <row r="340" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N340" s="1"/>
+    <row r="335" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N335" s="1"/>
     </row>
     <row r="341" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N341" s="1"/>
     </row>
-    <row r="343" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N343" s="1"/>
+    <row r="342" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N342" s="1"/>
     </row>
     <row r="344" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N344" s="1"/>
     </row>
-    <row r="349" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N349" s="1"/>
-    </row>
-    <row r="351" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N351" s="1"/>
+    <row r="345" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N345" s="1"/>
+    </row>
+    <row r="350" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N350" s="1"/>
     </row>
     <row r="352" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N352" s="1"/>
     </row>
-    <row r="354" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N354" s="1"/>
+    <row r="353" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N353" s="1"/>
     </row>
     <row r="355" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N355" s="1"/>
     </row>
-    <row r="363" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N363" s="1"/>
-    </row>
-    <row r="365" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N365" s="1"/>
-    </row>
-    <row r="367" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N367" s="1"/>
+    <row r="356" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N356" s="1"/>
+    </row>
+    <row r="364" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N364" s="1"/>
+    </row>
+    <row r="366" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N366" s="1"/>
     </row>
     <row r="368" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N368" s="1"/>
     </row>
-    <row r="373" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N373" s="1"/>
+    <row r="369" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N369" s="1"/>
     </row>
     <row r="374" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N374" s="1"/>
     </row>
-    <row r="376" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N376" s="1"/>
+    <row r="375" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N375" s="1"/>
     </row>
     <row r="377" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N377" s="1"/>
@@ -2012,17 +3246,17 @@
     <row r="378" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N378" s="1"/>
     </row>
-    <row r="381" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N381" s="1"/>
-    </row>
-    <row r="390" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N390" s="1"/>
+    <row r="379" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N379" s="1"/>
+    </row>
+    <row r="382" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N382" s="1"/>
     </row>
     <row r="391" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N391" s="1"/>
     </row>
-    <row r="394" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N394" s="1"/>
+    <row r="392" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N392" s="1"/>
     </row>
     <row r="395" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N395" s="1"/>
@@ -2030,20 +3264,20 @@
     <row r="396" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N396" s="1"/>
     </row>
-    <row r="398" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N398" s="1"/>
+    <row r="397" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N397" s="1"/>
     </row>
     <row r="399" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N399" s="1"/>
     </row>
-    <row r="401" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N401" s="1"/>
-    </row>
-    <row r="404" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N404" s="1"/>
-    </row>
-    <row r="406" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N406" s="1"/>
+    <row r="400" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N400" s="1"/>
+    </row>
+    <row r="402" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N402" s="1"/>
+    </row>
+    <row r="405" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N405" s="1"/>
     </row>
     <row r="407" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N407" s="1"/>
@@ -2051,20 +3285,20 @@
     <row r="408" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N408" s="1"/>
     </row>
-    <row r="411" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N411" s="1"/>
+    <row r="409" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N409" s="1"/>
     </row>
     <row r="412" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N412" s="1"/>
     </row>
-    <row r="415" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N415" s="1"/>
+    <row r="413" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N413" s="1"/>
     </row>
     <row r="416" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N416" s="1"/>
     </row>
-    <row r="419" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N419" s="1"/>
+    <row r="417" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N417" s="1"/>
     </row>
     <row r="420" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N420" s="1"/>
@@ -2072,44 +3306,44 @@
     <row r="421" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N421" s="1"/>
     </row>
-    <row r="424" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N424" s="1"/>
-    </row>
-    <row r="426" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N426" s="1"/>
-    </row>
-    <row r="432" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N432" s="1"/>
+    <row r="422" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N422" s="1"/>
+    </row>
+    <row r="425" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N425" s="1"/>
+    </row>
+    <row r="427" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N427" s="1"/>
     </row>
     <row r="433" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N433" s="1"/>
     </row>
-    <row r="438" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N438" s="1"/>
-    </row>
-    <row r="444" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N444" s="1"/>
+    <row r="434" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N434" s="1"/>
+    </row>
+    <row r="439" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N439" s="1"/>
     </row>
     <row r="445" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N445" s="1"/>
     </row>
-    <row r="454" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N454" s="1"/>
-    </row>
-    <row r="464" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="C464" s="1"/>
-    </row>
-    <row r="469" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N469" s="1"/>
-    </row>
-    <row r="476" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N476" s="1"/>
-    </row>
-    <row r="480" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N480" s="1"/>
-    </row>
-    <row r="491" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N491" s="1"/>
+    <row r="446" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N446" s="1"/>
+    </row>
+    <row r="455" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N455" s="1"/>
+    </row>
+    <row r="465" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C465" s="1"/>
+    </row>
+    <row r="470" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N470" s="1"/>
+    </row>
+    <row r="477" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N477" s="1"/>
+    </row>
+    <row r="481" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N481" s="1"/>
     </row>
     <row r="492" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N492" s="1"/>
@@ -2120,17 +3354,17 @@
     <row r="494" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N494" s="1"/>
     </row>
-    <row r="496" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N496" s="1"/>
-    </row>
-    <row r="498" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N498" s="1"/>
-    </row>
-    <row r="507" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N507" s="1"/>
-    </row>
-    <row r="509" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N509" s="1"/>
+    <row r="495" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N495" s="1"/>
+    </row>
+    <row r="497" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N497" s="1"/>
+    </row>
+    <row r="499" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N499" s="1"/>
+    </row>
+    <row r="508" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N508" s="1"/>
     </row>
     <row r="510" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N510" s="1"/>
@@ -2144,83 +3378,83 @@
     <row r="513" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N513" s="1"/>
     </row>
-    <row r="516" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N516" s="1"/>
+    <row r="514" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N514" s="1"/>
     </row>
     <row r="517" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N517" s="1"/>
     </row>
-    <row r="519" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N519" s="1"/>
-    </row>
-    <row r="525" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N525" s="1"/>
+    <row r="518" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N518" s="1"/>
+    </row>
+    <row r="520" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N520" s="1"/>
     </row>
     <row r="526" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N526" s="1"/>
     </row>
-    <row r="530" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N530" s="1"/>
+    <row r="527" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N527" s="1"/>
     </row>
     <row r="531" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N531" s="1"/>
     </row>
-    <row r="535" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N535" s="1"/>
-    </row>
-    <row r="537" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N537" s="1"/>
-    </row>
-    <row r="540" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N540" s="1"/>
-    </row>
-    <row r="557" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N557" s="1"/>
-    </row>
-    <row r="559" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N559" s="1"/>
+    <row r="532" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N532" s="1"/>
+    </row>
+    <row r="536" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N536" s="1"/>
+    </row>
+    <row r="538" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N538" s="1"/>
+    </row>
+    <row r="541" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N541" s="1"/>
+    </row>
+    <row r="558" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N558" s="1"/>
     </row>
     <row r="560" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N560" s="1"/>
     </row>
-    <row r="568" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N568" s="1"/>
-    </row>
-    <row r="571" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N571" s="1"/>
+    <row r="561" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N561" s="1"/>
+    </row>
+    <row r="569" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N569" s="1"/>
     </row>
     <row r="572" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N572" s="1"/>
     </row>
-    <row r="578" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N578" s="1"/>
-    </row>
-    <row r="581" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N581" s="1"/>
-    </row>
-    <row r="584" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N584" s="1"/>
+    <row r="573" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N573" s="1"/>
+    </row>
+    <row r="579" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N579" s="1"/>
+    </row>
+    <row r="582" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N582" s="1"/>
     </row>
     <row r="585" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N585" s="1"/>
     </row>
-    <row r="588" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N588" s="1"/>
-    </row>
-    <row r="594" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N594" s="1"/>
-    </row>
-    <row r="597" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N597" s="1"/>
-    </row>
-    <row r="599" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N599" s="1"/>
-    </row>
-    <row r="602" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N602" s="1"/>
-    </row>
-    <row r="610" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N610" s="1"/>
+    <row r="586" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N586" s="1"/>
+    </row>
+    <row r="589" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N589" s="1"/>
+    </row>
+    <row r="595" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N595" s="1"/>
+    </row>
+    <row r="598" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N598" s="1"/>
+    </row>
+    <row r="600" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N600" s="1"/>
+    </row>
+    <row r="603" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N603" s="1"/>
     </row>
     <row r="611" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N611" s="1"/>
@@ -2228,14 +3462,14 @@
     <row r="612" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N612" s="1"/>
     </row>
-    <row r="615" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N615" s="1"/>
+    <row r="613" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N613" s="1"/>
     </row>
     <row r="616" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N616" s="1"/>
     </row>
-    <row r="623" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N623" s="1"/>
+    <row r="617" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N617" s="1"/>
     </row>
     <row r="624" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N624" s="1"/>
@@ -2243,8 +3477,8 @@
     <row r="625" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N625" s="1"/>
     </row>
-    <row r="627" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N627" s="1"/>
+    <row r="626" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N626" s="1"/>
     </row>
     <row r="628" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N628" s="1"/>
@@ -2252,23 +3486,23 @@
     <row r="629" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N629" s="1"/>
     </row>
-    <row r="636" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N636" s="1"/>
-    </row>
-    <row r="640" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N640" s="1"/>
-    </row>
-    <row r="650" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N650" s="1"/>
+    <row r="630" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N630" s="1"/>
+    </row>
+    <row r="637" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N637" s="1"/>
+    </row>
+    <row r="641" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N641" s="1"/>
     </row>
     <row r="651" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N651" s="1"/>
     </row>
-    <row r="655" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N655" s="1"/>
-    </row>
-    <row r="658" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N658" s="1"/>
+    <row r="652" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N652" s="1"/>
+    </row>
+    <row r="656" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N656" s="1"/>
     </row>
     <row r="659" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N659" s="1"/>
@@ -2276,80 +3510,80 @@
     <row r="660" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N660" s="1"/>
     </row>
-    <row r="662" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N662" s="1"/>
-    </row>
-    <row r="665" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N665" s="1"/>
+    <row r="661" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N661" s="1"/>
+    </row>
+    <row r="663" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N663" s="1"/>
     </row>
     <row r="666" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N666" s="1"/>
     </row>
-    <row r="670" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N670" s="1"/>
+    <row r="667" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N667" s="1"/>
     </row>
     <row r="671" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N671" s="1"/>
     </row>
-    <row r="677" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N677" s="1"/>
-    </row>
-    <row r="680" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N680" s="1"/>
+    <row r="672" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N672" s="1"/>
+    </row>
+    <row r="678" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N678" s="1"/>
     </row>
     <row r="681" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N681" s="1"/>
     </row>
-    <row r="689" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N689" s="1"/>
-    </row>
-    <row r="692" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N692" s="1"/>
+    <row r="682" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N682" s="1"/>
+    </row>
+    <row r="690" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N690" s="1"/>
     </row>
     <row r="693" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N693" s="1"/>
     </row>
-    <row r="698" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N698" s="1"/>
-    </row>
-    <row r="705" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N705" s="1"/>
-    </row>
-    <row r="707" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N707" s="1"/>
-    </row>
-    <row r="709" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N709" s="1"/>
+    <row r="694" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N694" s="1"/>
+    </row>
+    <row r="699" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N699" s="1"/>
+    </row>
+    <row r="706" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N706" s="1"/>
+    </row>
+    <row r="708" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N708" s="1"/>
     </row>
     <row r="710" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N710" s="1"/>
     </row>
-    <row r="713" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N713" s="1"/>
+    <row r="711" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N711" s="1"/>
     </row>
     <row r="714" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N714" s="1"/>
     </row>
-    <row r="717" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N717" s="1"/>
-    </row>
-    <row r="720" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N720" s="1"/>
-    </row>
-    <row r="726" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N726" s="1"/>
+    <row r="715" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N715" s="1"/>
+    </row>
+    <row r="718" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N718" s="1"/>
+    </row>
+    <row r="721" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N721" s="1"/>
     </row>
     <row r="727" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N727" s="1"/>
     </row>
-    <row r="730" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N730" s="1"/>
-    </row>
-    <row r="740" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N740" s="1"/>
-    </row>
-    <row r="743" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N743" s="1"/>
+    <row r="728" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N728" s="1"/>
+    </row>
+    <row r="731" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N731" s="1"/>
+    </row>
+    <row r="741" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N741" s="1"/>
     </row>
     <row r="744" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N744" s="1"/>
@@ -2360,11 +3594,11 @@
     <row r="746" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N746" s="1"/>
     </row>
-    <row r="751" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N751" s="1"/>
-    </row>
-    <row r="756" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N756" s="1"/>
+    <row r="747" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N747" s="1"/>
+    </row>
+    <row r="752" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N752" s="1"/>
     </row>
     <row r="757" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N757" s="1"/>
@@ -2372,104 +3606,104 @@
     <row r="758" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N758" s="1"/>
     </row>
-    <row r="761" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N761" s="1"/>
-    </row>
-    <row r="765" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N765" s="1"/>
-    </row>
-    <row r="769" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N769" s="1"/>
-    </row>
-    <row r="777" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N777" s="1"/>
-    </row>
-    <row r="782" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N782" s="1"/>
-    </row>
-    <row r="788" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N788" s="1"/>
-    </row>
-    <row r="790" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N790" s="1"/>
-    </row>
-    <row r="796" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N796" s="1"/>
+    <row r="759" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N759" s="1"/>
+    </row>
+    <row r="762" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N762" s="1"/>
+    </row>
+    <row r="766" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N766" s="1"/>
+    </row>
+    <row r="770" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N770" s="1"/>
+    </row>
+    <row r="778" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N778" s="1"/>
+    </row>
+    <row r="783" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N783" s="1"/>
+    </row>
+    <row r="789" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N789" s="1"/>
+    </row>
+    <row r="791" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N791" s="1"/>
     </row>
     <row r="797" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N797" s="1"/>
     </row>
-    <row r="802" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N802" s="1"/>
-    </row>
-    <row r="807" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N807" s="1"/>
-    </row>
-    <row r="823" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N823" s="1"/>
-    </row>
-    <row r="828" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N828" s="1"/>
-    </row>
-    <row r="839" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N839" s="1"/>
+    <row r="798" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N798" s="1"/>
+    </row>
+    <row r="803" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N803" s="1"/>
+    </row>
+    <row r="808" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N808" s="1"/>
+    </row>
+    <row r="824" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N824" s="1"/>
+    </row>
+    <row r="829" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N829" s="1"/>
     </row>
     <row r="840" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N840" s="1"/>
     </row>
-    <row r="842" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N842" s="1"/>
-    </row>
-    <row r="846" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N846" s="1"/>
-    </row>
-    <row r="859" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N859" s="1"/>
-    </row>
-    <row r="863" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N863" s="1"/>
-    </row>
-    <row r="869" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N869" s="1"/>
-    </row>
-    <row r="872" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N872" s="1"/>
+    <row r="841" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N841" s="1"/>
+    </row>
+    <row r="843" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N843" s="1"/>
+    </row>
+    <row r="847" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N847" s="1"/>
+    </row>
+    <row r="860" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N860" s="1"/>
+    </row>
+    <row r="864" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N864" s="1"/>
+    </row>
+    <row r="870" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N870" s="1"/>
     </row>
     <row r="873" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N873" s="1"/>
     </row>
-    <row r="876" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N876" s="1"/>
-    </row>
-    <row r="879" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N879" s="1"/>
+    <row r="874" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N874" s="1"/>
+    </row>
+    <row r="877" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N877" s="1"/>
     </row>
     <row r="880" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N880" s="1"/>
     </row>
-    <row r="887" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N887" s="1"/>
+    <row r="881" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N881" s="1"/>
     </row>
     <row r="888" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N888" s="1"/>
     </row>
-    <row r="891" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N891" s="1"/>
-    </row>
-    <row r="894" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N894" s="1"/>
+    <row r="889" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N889" s="1"/>
+    </row>
+    <row r="892" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N892" s="1"/>
     </row>
     <row r="895" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N895" s="1"/>
     </row>
-    <row r="901" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N901" s="1"/>
+    <row r="896" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N896" s="1"/>
     </row>
     <row r="902" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N902" s="1"/>
     </row>
-    <row r="910" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N910" s="1"/>
+    <row r="903" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N903" s="1"/>
     </row>
     <row r="911" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N911" s="1"/>
@@ -2480,53 +3714,53 @@
     <row r="913" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N913" s="1"/>
     </row>
-    <row r="915" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N915" s="1"/>
-    </row>
-    <row r="921" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N921" s="1"/>
-    </row>
-    <row r="925" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N925" s="1"/>
+    <row r="914" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N914" s="1"/>
+    </row>
+    <row r="916" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N916" s="1"/>
+    </row>
+    <row r="922" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N922" s="1"/>
     </row>
     <row r="926" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N926" s="1"/>
     </row>
-    <row r="937" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N937" s="1"/>
-    </row>
-    <row r="940" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N940" s="1"/>
-    </row>
-    <row r="943" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N943" s="1"/>
-    </row>
-    <row r="946" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N946" s="1"/>
+    <row r="927" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N927" s="1"/>
+    </row>
+    <row r="938" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N938" s="1"/>
+    </row>
+    <row r="941" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N941" s="1"/>
+    </row>
+    <row r="944" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N944" s="1"/>
     </row>
     <row r="947" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N947" s="1"/>
     </row>
-    <row r="952" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N952" s="1"/>
-    </row>
-    <row r="955" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N955" s="1"/>
-    </row>
-    <row r="959" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N959" s="1"/>
-    </row>
-    <row r="976" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N976" s="1"/>
-    </row>
-    <row r="980" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N980" s="1"/>
-    </row>
-    <row r="989" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N989" s="1"/>
-    </row>
-    <row r="992" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N992" s="1"/>
+    <row r="948" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N948" s="1"/>
+    </row>
+    <row r="953" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N953" s="1"/>
+    </row>
+    <row r="956" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N956" s="1"/>
+    </row>
+    <row r="960" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N960" s="1"/>
+    </row>
+    <row r="977" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N977" s="1"/>
+    </row>
+    <row r="981" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N981" s="1"/>
+    </row>
+    <row r="990" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N990" s="1"/>
     </row>
     <row r="993" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N993" s="1"/>
@@ -2534,11 +3768,11 @@
     <row r="994" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N994" s="1"/>
     </row>
-    <row r="1002" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1002" s="1"/>
-    </row>
-    <row r="1007" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1007" s="1"/>
+    <row r="995" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N995" s="1"/>
+    </row>
+    <row r="1003" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1003" s="1"/>
     </row>
     <row r="1008" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1008" s="1"/>
@@ -2546,149 +3780,149 @@
     <row r="1009" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1009" s="1"/>
     </row>
-    <row r="1012" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1012" s="1"/>
-    </row>
-    <row r="1015" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1015" s="1"/>
+    <row r="1010" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1010" s="1"/>
+    </row>
+    <row r="1013" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1013" s="1"/>
     </row>
     <row r="1016" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1016" s="1"/>
     </row>
-    <row r="1020" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1020" s="1"/>
-    </row>
-    <row r="1022" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1022" s="1"/>
+    <row r="1017" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1017" s="1"/>
+    </row>
+    <row r="1021" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1021" s="1"/>
     </row>
     <row r="1023" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1023" s="1"/>
     </row>
-    <row r="1029" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1029" s="1"/>
-    </row>
-    <row r="1033" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1033" s="1"/>
-    </row>
-    <row r="1036" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1036" s="1"/>
-    </row>
-    <row r="1040" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1040" s="1"/>
+    <row r="1024" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1024" s="1"/>
+    </row>
+    <row r="1030" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1030" s="1"/>
+    </row>
+    <row r="1034" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1034" s="1"/>
+    </row>
+    <row r="1037" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1037" s="1"/>
     </row>
     <row r="1041" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1041" s="1"/>
     </row>
-    <row r="1043" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1043" s="1"/>
+    <row r="1042" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1042" s="1"/>
     </row>
     <row r="1044" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1044" s="1"/>
     </row>
-    <row r="1046" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1046" s="1"/>
-    </row>
-    <row r="1049" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1049" s="1"/>
-    </row>
-    <row r="1054" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1054" s="1"/>
-    </row>
-    <row r="1056" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1056" s="1"/>
-    </row>
-    <row r="1060" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1060" s="1"/>
-    </row>
-    <row r="1062" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1062" s="1"/>
+    <row r="1045" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1045" s="1"/>
+    </row>
+    <row r="1047" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1047" s="1"/>
+    </row>
+    <row r="1050" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1050" s="1"/>
+    </row>
+    <row r="1055" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1055" s="1"/>
+    </row>
+    <row r="1057" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1057" s="1"/>
+    </row>
+    <row r="1061" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1061" s="1"/>
     </row>
     <row r="1063" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1063" s="1"/>
     </row>
-    <row r="1065" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1065" s="1"/>
-    </row>
-    <row r="1067" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1067" s="1"/>
-    </row>
-    <row r="1070" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1070" s="1"/>
-    </row>
-    <row r="1072" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1072" s="1"/>
-    </row>
-    <row r="1074" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1074" s="1"/>
-    </row>
-    <row r="1092" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1092" s="1"/>
-    </row>
-    <row r="1099" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1099" s="1"/>
-    </row>
-    <row r="1101" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1101" s="1"/>
-    </row>
-    <row r="1104" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1104" s="1"/>
-    </row>
-    <row r="1115" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1115" s="1"/>
-    </row>
-    <row r="1118" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1118" s="1"/>
-    </row>
-    <row r="1124" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1124" s="1"/>
+    <row r="1064" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1064" s="1"/>
+    </row>
+    <row r="1066" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1066" s="1"/>
+    </row>
+    <row r="1068" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1068" s="1"/>
+    </row>
+    <row r="1071" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1071" s="1"/>
+    </row>
+    <row r="1073" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1073" s="1"/>
+    </row>
+    <row r="1075" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1075" s="1"/>
+    </row>
+    <row r="1093" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1093" s="1"/>
+    </row>
+    <row r="1100" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1100" s="1"/>
+    </row>
+    <row r="1102" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1102" s="1"/>
+    </row>
+    <row r="1105" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1105" s="1"/>
+    </row>
+    <row r="1116" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1116" s="1"/>
+    </row>
+    <row r="1119" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1119" s="1"/>
     </row>
     <row r="1125" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1125" s="1"/>
     </row>
-    <row r="1129" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1129" s="1"/>
-    </row>
-    <row r="1132" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1132" s="1"/>
+    <row r="1126" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1126" s="1"/>
+    </row>
+    <row r="1130" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1130" s="1"/>
     </row>
     <row r="1133" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1133" s="1"/>
     </row>
-    <row r="1135" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1135" s="1"/>
-    </row>
-    <row r="1139" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1139" s="1"/>
-    </row>
-    <row r="1141" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1141" s="1"/>
-    </row>
-    <row r="1144" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1144" s="1"/>
-    </row>
-    <row r="1150" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1150" s="1"/>
+    <row r="1134" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1134" s="1"/>
+    </row>
+    <row r="1136" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1136" s="1"/>
+    </row>
+    <row r="1140" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1140" s="1"/>
+    </row>
+    <row r="1142" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1142" s="1"/>
+    </row>
+    <row r="1145" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1145" s="1"/>
     </row>
     <row r="1151" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1151" s="1"/>
     </row>
-    <row r="1154" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1154" s="1"/>
-    </row>
-    <row r="1157" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1157" s="1"/>
-    </row>
-    <row r="1169" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1169" s="1"/>
+    <row r="1152" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1152" s="1"/>
+    </row>
+    <row r="1155" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1155" s="1"/>
+    </row>
+    <row r="1158" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1158" s="1"/>
     </row>
     <row r="1170" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1170" s="1"/>
     </row>
-    <row r="1172" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1172" s="1"/>
-    </row>
-    <row r="1177" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1177" s="1"/>
+    <row r="1171" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1171" s="1"/>
+    </row>
+    <row r="1173" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1173" s="1"/>
     </row>
     <row r="1178" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1178" s="1"/>
@@ -2696,11 +3930,11 @@
     <row r="1179" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1179" s="1"/>
     </row>
-    <row r="1188" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1188" s="1"/>
-    </row>
-    <row r="1193" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1193" s="1"/>
+    <row r="1180" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1180" s="1"/>
+    </row>
+    <row r="1189" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1189" s="1"/>
     </row>
     <row r="1194" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1194" s="1"/>
@@ -2711,32 +3945,32 @@
     <row r="1196" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1196" s="1"/>
     </row>
-    <row r="1200" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1200" s="1"/>
+    <row r="1197" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1197" s="1"/>
     </row>
     <row r="1201" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1201" s="1"/>
     </row>
-    <row r="1216" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1216" s="1"/>
-    </row>
-    <row r="1219" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1219" s="1"/>
+    <row r="1202" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1202" s="1"/>
+    </row>
+    <row r="1217" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1217" s="1"/>
     </row>
     <row r="1220" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1220" s="1"/>
     </row>
-    <row r="1222" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1222" s="1"/>
+    <row r="1221" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1221" s="1"/>
     </row>
     <row r="1223" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1223" s="1"/>
     </row>
-    <row r="1235" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1235" s="1"/>
-    </row>
-    <row r="1238" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1238" s="1"/>
+    <row r="1224" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1224" s="1"/>
+    </row>
+    <row r="1236" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1236" s="1"/>
     </row>
     <row r="1239" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1239" s="1"/>
@@ -2744,74 +3978,74 @@
     <row r="1240" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1240" s="1"/>
     </row>
-    <row r="1243" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1243" s="1"/>
-    </row>
-    <row r="1256" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1256" s="1"/>
-    </row>
-    <row r="1261" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1261" s="1"/>
-    </row>
-    <row r="1273" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1273" s="1"/>
-    </row>
-    <row r="1275" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1275" s="1"/>
+    <row r="1241" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1241" s="1"/>
+    </row>
+    <row r="1244" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1244" s="1"/>
+    </row>
+    <row r="1257" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1257" s="1"/>
+    </row>
+    <row r="1262" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1262" s="1"/>
+    </row>
+    <row r="1274" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1274" s="1"/>
     </row>
     <row r="1276" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1276" s="1"/>
     </row>
-    <row r="1283" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1283" s="1"/>
-    </row>
-    <row r="1287" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1287" s="1"/>
-    </row>
-    <row r="1291" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1291" s="1"/>
-    </row>
-    <row r="1298" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1298" s="1"/>
+    <row r="1277" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1277" s="1"/>
+    </row>
+    <row r="1284" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1284" s="1"/>
+    </row>
+    <row r="1288" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1288" s="1"/>
+    </row>
+    <row r="1292" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1292" s="1"/>
     </row>
     <row r="1299" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1299" s="1"/>
     </row>
-    <row r="1302" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1302" s="1"/>
-    </row>
-    <row r="1304" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1304" s="1"/>
-    </row>
-    <row r="1308" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1308" s="1"/>
-    </row>
-    <row r="1317" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1317" s="1"/>
-    </row>
-    <row r="1319" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1319" s="1"/>
-    </row>
-    <row r="1322" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1322" s="1"/>
-    </row>
-    <row r="1324" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1324" s="1"/>
-    </row>
-    <row r="1326" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1326" s="1"/>
-    </row>
-    <row r="1330" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1330" s="1"/>
-    </row>
-    <row r="1337" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1337" s="1"/>
-    </row>
-    <row r="1342" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1342" s="1"/>
-    </row>
-    <row r="1349" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1349" s="1"/>
+    <row r="1300" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1300" s="1"/>
+    </row>
+    <row r="1303" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1303" s="1"/>
+    </row>
+    <row r="1305" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1305" s="1"/>
+    </row>
+    <row r="1309" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1309" s="1"/>
+    </row>
+    <row r="1318" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1318" s="1"/>
+    </row>
+    <row r="1320" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1320" s="1"/>
+    </row>
+    <row r="1323" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1323" s="1"/>
+    </row>
+    <row r="1325" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1325" s="1"/>
+    </row>
+    <row r="1327" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1327" s="1"/>
+    </row>
+    <row r="1331" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1331" s="1"/>
+    </row>
+    <row r="1338" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1338" s="1"/>
+    </row>
+    <row r="1343" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1343" s="1"/>
     </row>
     <row r="1350" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1350" s="1"/>
@@ -2819,128 +4053,128 @@
     <row r="1351" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1351" s="1"/>
     </row>
-    <row r="1355" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1355" s="1"/>
-    </row>
-    <row r="1359" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1359" s="1"/>
+    <row r="1352" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1352" s="1"/>
+    </row>
+    <row r="1356" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1356" s="1"/>
     </row>
     <row r="1360" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1360" s="1"/>
     </row>
-    <row r="1362" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1362" s="1"/>
-    </row>
-    <row r="1364" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1364" s="1"/>
+    <row r="1361" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1361" s="1"/>
+    </row>
+    <row r="1363" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1363" s="1"/>
     </row>
     <row r="1365" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1365" s="1"/>
     </row>
-    <row r="1374" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1374" s="1"/>
-    </row>
-    <row r="1377" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1377" s="1"/>
-    </row>
-    <row r="1380" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1380" s="1"/>
-    </row>
-    <row r="1382" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1382" s="1"/>
-    </row>
-    <row r="1384" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1384" s="1"/>
+    <row r="1366" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1366" s="1"/>
+    </row>
+    <row r="1375" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1375" s="1"/>
+    </row>
+    <row r="1378" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1378" s="1"/>
+    </row>
+    <row r="1381" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1381" s="1"/>
+    </row>
+    <row r="1383" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1383" s="1"/>
     </row>
     <row r="1385" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1385" s="1"/>
     </row>
-    <row r="1387" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1387" s="1"/>
-    </row>
-    <row r="1391" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1391" s="1"/>
-    </row>
-    <row r="1401" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1401" s="1"/>
-    </row>
-    <row r="1404" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1404" s="1"/>
-    </row>
-    <row r="1409" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1409" s="1"/>
-    </row>
-    <row r="1422" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1422" s="1"/>
-    </row>
-    <row r="1424" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1424" s="1"/>
-    </row>
-    <row r="1431" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1431" s="1"/>
-    </row>
-    <row r="1433" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1433" s="1"/>
-    </row>
-    <row r="1435" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1435" s="1"/>
-    </row>
-    <row r="1439" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1439" s="1"/>
-    </row>
-    <row r="1441" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1441" s="1"/>
-    </row>
-    <row r="1443" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1443" s="1"/>
+    <row r="1386" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1386" s="1"/>
+    </row>
+    <row r="1388" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1388" s="1"/>
+    </row>
+    <row r="1392" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1392" s="1"/>
+    </row>
+    <row r="1402" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1402" s="1"/>
+    </row>
+    <row r="1405" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1405" s="1"/>
+    </row>
+    <row r="1410" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1410" s="1"/>
+    </row>
+    <row r="1423" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1423" s="1"/>
+    </row>
+    <row r="1425" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1425" s="1"/>
+    </row>
+    <row r="1432" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1432" s="1"/>
+    </row>
+    <row r="1434" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1434" s="1"/>
+    </row>
+    <row r="1436" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1436" s="1"/>
+    </row>
+    <row r="1440" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1440" s="1"/>
+    </row>
+    <row r="1442" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1442" s="1"/>
     </row>
     <row r="1444" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1444" s="1"/>
     </row>
-    <row r="1448" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1448" s="1"/>
-    </row>
-    <row r="1454" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1454" s="1"/>
+    <row r="1445" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1445" s="1"/>
+    </row>
+    <row r="1449" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1449" s="1"/>
     </row>
     <row r="1455" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1455" s="1"/>
     </row>
-    <row r="1460" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1460" s="1"/>
-    </row>
-    <row r="1463" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1463" s="1"/>
-    </row>
-    <row r="1466" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1466" s="1"/>
-    </row>
-    <row r="1472" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1472" s="1"/>
-    </row>
-    <row r="1475" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1475" s="1"/>
+    <row r="1456" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1456" s="1"/>
+    </row>
+    <row r="1461" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1461" s="1"/>
+    </row>
+    <row r="1464" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1464" s="1"/>
+    </row>
+    <row r="1467" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1467" s="1"/>
+    </row>
+    <row r="1473" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1473" s="1"/>
     </row>
     <row r="1476" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1476" s="1"/>
     </row>
-    <row r="1480" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1480" s="1"/>
-    </row>
-    <row r="1489" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1489" s="1"/>
-    </row>
-    <row r="1493" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1493" s="1"/>
-    </row>
-    <row r="1496" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1496" s="1"/>
-    </row>
-    <row r="1498" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1498" s="1"/>
-    </row>
-    <row r="1508" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1508" s="1"/>
+    <row r="1477" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1477" s="1"/>
+    </row>
+    <row r="1481" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1481" s="1"/>
+    </row>
+    <row r="1490" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1490" s="1"/>
+    </row>
+    <row r="1494" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1494" s="1"/>
+    </row>
+    <row r="1497" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1497" s="1"/>
+    </row>
+    <row r="1499" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1499" s="1"/>
     </row>
     <row r="1509" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1509" s="1"/>
@@ -2948,65 +4182,65 @@
     <row r="1510" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1510" s="1"/>
     </row>
-    <row r="1512" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1512" s="1"/>
-    </row>
-    <row r="1517" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1517" s="1"/>
-    </row>
-    <row r="1519" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1519" s="1"/>
-    </row>
-    <row r="1521" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1521" s="1"/>
-    </row>
-    <row r="1530" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1530" s="1"/>
-    </row>
-    <row r="1536" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1536" s="1"/>
-    </row>
-    <row r="1542" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1542" s="1"/>
+    <row r="1511" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1511" s="1"/>
+    </row>
+    <row r="1513" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1513" s="1"/>
+    </row>
+    <row r="1518" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1518" s="1"/>
+    </row>
+    <row r="1520" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1520" s="1"/>
+    </row>
+    <row r="1522" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1522" s="1"/>
+    </row>
+    <row r="1531" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1531" s="1"/>
+    </row>
+    <row r="1537" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1537" s="1"/>
     </row>
     <row r="1543" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1543" s="1"/>
     </row>
-    <row r="1546" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1546" s="1"/>
-    </row>
-    <row r="1556" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1556" s="1"/>
-    </row>
-    <row r="1562" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1562" s="1"/>
+    <row r="1544" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1544" s="1"/>
+    </row>
+    <row r="1547" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1547" s="1"/>
+    </row>
+    <row r="1557" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1557" s="1"/>
     </row>
     <row r="1563" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1563" s="1"/>
     </row>
-    <row r="1566" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1566" s="1"/>
+    <row r="1564" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1564" s="1"/>
     </row>
     <row r="1567" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1567" s="1"/>
     </row>
-    <row r="1570" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1570" s="1"/>
+    <row r="1568" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1568" s="1"/>
     </row>
     <row r="1571" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1571" s="1"/>
     </row>
-    <row r="1573" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1573" s="1"/>
-    </row>
-    <row r="1577" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1577" s="1"/>
-    </row>
-    <row r="1582" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1582" s="1"/>
-    </row>
-    <row r="1586" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1586" s="1"/>
+    <row r="1572" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1572" s="1"/>
+    </row>
+    <row r="1574" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1574" s="1"/>
+    </row>
+    <row r="1578" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1578" s="1"/>
+    </row>
+    <row r="1583" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1583" s="1"/>
     </row>
     <row r="1587" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1587" s="1"/>
@@ -3014,32 +4248,32 @@
     <row r="1588" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1588" s="1"/>
     </row>
-    <row r="1591" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1591" s="1"/>
-    </row>
-    <row r="1599" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1599" s="1"/>
-    </row>
-    <row r="1601" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1601" s="1"/>
-    </row>
-    <row r="1608" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1608" s="1"/>
-    </row>
-    <row r="1610" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1610" s="1"/>
-    </row>
-    <row r="1612" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1612" s="1"/>
-    </row>
-    <row r="1616" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1616" s="1"/>
-    </row>
-    <row r="1625" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1625" s="1"/>
-    </row>
-    <row r="1627" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1627" s="1"/>
+    <row r="1589" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1589" s="1"/>
+    </row>
+    <row r="1592" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1592" s="1"/>
+    </row>
+    <row r="1600" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1600" s="1"/>
+    </row>
+    <row r="1602" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1602" s="1"/>
+    </row>
+    <row r="1609" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1609" s="1"/>
+    </row>
+    <row r="1611" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1611" s="1"/>
+    </row>
+    <row r="1613" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1613" s="1"/>
+    </row>
+    <row r="1617" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1617" s="1"/>
+    </row>
+    <row r="1626" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1626" s="1"/>
     </row>
     <row r="1628" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1628" s="1"/>
@@ -3047,38 +4281,38 @@
     <row r="1629" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1629" s="1"/>
     </row>
-    <row r="1633" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1633" s="1"/>
-    </row>
-    <row r="1637" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1637" s="1"/>
-    </row>
-    <row r="1640" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1640" s="1"/>
-    </row>
-    <row r="1642" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1642" s="1"/>
+    <row r="1630" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1630" s="1"/>
+    </row>
+    <row r="1634" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1634" s="1"/>
+    </row>
+    <row r="1638" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1638" s="1"/>
+    </row>
+    <row r="1641" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1641" s="1"/>
     </row>
     <row r="1643" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1643" s="1"/>
     </row>
-    <row r="1656" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1656" s="1"/>
-    </row>
-    <row r="1660" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1660" s="1"/>
-    </row>
-    <row r="1663" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1663" s="1"/>
+    <row r="1644" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1644" s="1"/>
+    </row>
+    <row r="1657" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1657" s="1"/>
+    </row>
+    <row r="1661" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1661" s="1"/>
     </row>
     <row r="1664" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1664" s="1"/>
     </row>
-    <row r="1669" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1669" s="1"/>
-    </row>
-    <row r="1671" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1671" s="1"/>
+    <row r="1665" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1665" s="1"/>
+    </row>
+    <row r="1670" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1670" s="1"/>
     </row>
     <row r="1672" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1672" s="1"/>
@@ -3089,80 +4323,80 @@
     <row r="1674" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1674" s="1"/>
     </row>
-    <row r="1676" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1676" s="1"/>
-    </row>
-    <row r="1682" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1682" s="1"/>
-    </row>
-    <row r="1684" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1684" s="1"/>
-    </row>
-    <row r="1692" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1692" s="1"/>
+    <row r="1675" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1675" s="1"/>
+    </row>
+    <row r="1677" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1677" s="1"/>
+    </row>
+    <row r="1683" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1683" s="1"/>
+    </row>
+    <row r="1685" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1685" s="1"/>
     </row>
     <row r="1693" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1693" s="1"/>
     </row>
-    <row r="1695" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1695" s="1"/>
-    </row>
-    <row r="1698" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1698" s="1"/>
-    </row>
-    <row r="1700" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1700" s="1"/>
-    </row>
-    <row r="1705" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1705" s="1"/>
-    </row>
-    <row r="1712" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1712" s="1"/>
-    </row>
-    <row r="1716" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1716" s="1"/>
-    </row>
-    <row r="1723" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1723" s="1"/>
-    </row>
-    <row r="1731" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1731" s="1"/>
-    </row>
-    <row r="1734" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1734" s="1"/>
-    </row>
-    <row r="1736" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1736" s="1"/>
-    </row>
-    <row r="1739" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1739" s="1"/>
+    <row r="1694" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1694" s="1"/>
+    </row>
+    <row r="1696" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1696" s="1"/>
+    </row>
+    <row r="1699" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1699" s="1"/>
+    </row>
+    <row r="1701" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1701" s="1"/>
+    </row>
+    <row r="1706" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1706" s="1"/>
+    </row>
+    <row r="1713" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1713" s="1"/>
+    </row>
+    <row r="1717" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1717" s="1"/>
+    </row>
+    <row r="1724" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1724" s="1"/>
+    </row>
+    <row r="1732" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1732" s="1"/>
+    </row>
+    <row r="1735" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1735" s="1"/>
+    </row>
+    <row r="1737" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1737" s="1"/>
     </row>
     <row r="1740" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1740" s="1"/>
     </row>
-    <row r="1748" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1748" s="1"/>
+    <row r="1741" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1741" s="1"/>
     </row>
     <row r="1749" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1749" s="1"/>
     </row>
-    <row r="1751" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1751" s="1"/>
-    </row>
-    <row r="1756" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1756" s="1"/>
+    <row r="1750" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1750" s="1"/>
+    </row>
+    <row r="1752" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1752" s="1"/>
     </row>
     <row r="1757" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1757" s="1"/>
     </row>
-    <row r="1759" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1759" s="1"/>
-    </row>
-    <row r="1764" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1764" s="1"/>
-    </row>
-    <row r="1766" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1766" s="1"/>
+    <row r="1758" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1758" s="1"/>
+    </row>
+    <row r="1760" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1760" s="1"/>
+    </row>
+    <row r="1765" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1765" s="1"/>
     </row>
     <row r="1767" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1767" s="1"/>
@@ -3176,59 +4410,59 @@
     <row r="1770" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1770" s="1"/>
     </row>
-    <row r="1772" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1772" s="1"/>
-    </row>
-    <row r="1774" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1774" s="1"/>
-    </row>
-    <row r="1776" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1776" s="1"/>
-    </row>
-    <row r="1784" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1784" s="1"/>
-    </row>
-    <row r="1794" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1794" s="1"/>
-    </row>
-    <row r="1796" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1796" s="1"/>
-    </row>
-    <row r="1799" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1799" s="1"/>
-    </row>
-    <row r="1810" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1810" s="1"/>
-    </row>
-    <row r="1813" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1813" s="1"/>
+    <row r="1771" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1771" s="1"/>
+    </row>
+    <row r="1773" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1773" s="1"/>
+    </row>
+    <row r="1775" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1775" s="1"/>
+    </row>
+    <row r="1777" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1777" s="1"/>
+    </row>
+    <row r="1785" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1785" s="1"/>
+    </row>
+    <row r="1795" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1795" s="1"/>
+    </row>
+    <row r="1797" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1797" s="1"/>
+    </row>
+    <row r="1800" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1800" s="1"/>
+    </row>
+    <row r="1811" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1811" s="1"/>
     </row>
     <row r="1814" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1814" s="1"/>
     </row>
-    <row r="1819" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1819" s="1"/>
-    </row>
-    <row r="1823" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1823" s="1"/>
-    </row>
-    <row r="1825" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1825" s="1"/>
-    </row>
-    <row r="1827" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1827" s="1"/>
+    <row r="1815" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1815" s="1"/>
+    </row>
+    <row r="1820" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1820" s="1"/>
+    </row>
+    <row r="1824" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1824" s="1"/>
+    </row>
+    <row r="1826" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1826" s="1"/>
     </row>
     <row r="1828" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1828" s="1"/>
     </row>
-    <row r="1830" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1830" s="1"/>
-    </row>
-    <row r="1834" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1834" s="1"/>
-    </row>
-    <row r="1846" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1846" s="1"/>
+    <row r="1829" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1829" s="1"/>
+    </row>
+    <row r="1831" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1831" s="1"/>
+    </row>
+    <row r="1835" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1835" s="1"/>
     </row>
     <row r="1847" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1847" s="1"/>
@@ -3236,20 +4470,20 @@
     <row r="1848" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1848" s="1"/>
     </row>
-    <row r="1851" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1851" s="1"/>
-    </row>
-    <row r="1854" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1854" s="1"/>
-    </row>
-    <row r="1860" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1860" s="1"/>
-    </row>
-    <row r="1865" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1865" s="1"/>
-    </row>
-    <row r="1867" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1867" s="1"/>
+    <row r="1849" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1849" s="1"/>
+    </row>
+    <row r="1852" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1852" s="1"/>
+    </row>
+    <row r="1855" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1855" s="1"/>
+    </row>
+    <row r="1861" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1861" s="1"/>
+    </row>
+    <row r="1866" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1866" s="1"/>
     </row>
     <row r="1868" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1868" s="1"/>
@@ -3257,41 +4491,41 @@
     <row r="1869" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1869" s="1"/>
     </row>
-    <row r="1873" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1873" s="1"/>
+    <row r="1870" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1870" s="1"/>
     </row>
     <row r="1874" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1874" s="1"/>
     </row>
-    <row r="1880" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1880" s="1"/>
-    </row>
-    <row r="1885" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1885" s="1"/>
-    </row>
-    <row r="1888" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1888" s="1"/>
+    <row r="1875" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1875" s="1"/>
+    </row>
+    <row r="1881" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1881" s="1"/>
+    </row>
+    <row r="1886" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1886" s="1"/>
     </row>
     <row r="1889" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1889" s="1"/>
     </row>
-    <row r="1898" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1898" s="1"/>
-    </row>
-    <row r="1908" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1908" s="1"/>
-    </row>
-    <row r="1913" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1913" s="1"/>
-    </row>
-    <row r="1915" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1915" s="1"/>
-    </row>
-    <row r="1917" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1917" s="1"/>
-    </row>
-    <row r="1925" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1925" s="1"/>
+    <row r="1890" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1890" s="1"/>
+    </row>
+    <row r="1899" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1899" s="1"/>
+    </row>
+    <row r="1909" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1909" s="1"/>
+    </row>
+    <row r="1914" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1914" s="1"/>
+    </row>
+    <row r="1916" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1916" s="1"/>
+    </row>
+    <row r="1918" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1918" s="1"/>
     </row>
     <row r="1926" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1926" s="1"/>
@@ -3302,29 +4536,29 @@
     <row r="1928" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1928" s="1"/>
     </row>
-    <row r="1931" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1931" s="1"/>
-    </row>
-    <row r="1939" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1939" s="1"/>
-    </row>
-    <row r="1944" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1944" s="1"/>
-    </row>
-    <row r="1946" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1946" s="1"/>
+    <row r="1929" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1929" s="1"/>
+    </row>
+    <row r="1932" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1932" s="1"/>
+    </row>
+    <row r="1940" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1940" s="1"/>
+    </row>
+    <row r="1945" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1945" s="1"/>
     </row>
     <row r="1947" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1947" s="1"/>
     </row>
-    <row r="1953" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1953" s="1"/>
-    </row>
-    <row r="1955" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1955" s="1"/>
-    </row>
-    <row r="1957" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1957" s="1"/>
+    <row r="1948" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1948" s="1"/>
+    </row>
+    <row r="1954" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1954" s="1"/>
+    </row>
+    <row r="1956" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1956" s="1"/>
     </row>
     <row r="1958" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1958" s="1"/>
@@ -3332,44 +4566,44 @@
     <row r="1959" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1959" s="1"/>
     </row>
-    <row r="1968" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1968" s="1"/>
-    </row>
-    <row r="1971" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1971" s="1"/>
+    <row r="1960" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1960" s="1"/>
+    </row>
+    <row r="1969" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1969" s="1"/>
     </row>
     <row r="1972" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1972" s="1"/>
     </row>
-    <row r="1974" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1974" s="1"/>
-    </row>
-    <row r="1988" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1988" s="1"/>
-    </row>
-    <row r="1993" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1993" s="1"/>
-    </row>
-    <row r="1995" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1995" s="1"/>
+    <row r="1973" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1973" s="1"/>
+    </row>
+    <row r="1975" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1975" s="1"/>
+    </row>
+    <row r="1989" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1989" s="1"/>
+    </row>
+    <row r="1994" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1994" s="1"/>
     </row>
     <row r="1996" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1996" s="1"/>
     </row>
-    <row r="1998" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N1998" s="1"/>
-    </row>
-    <row r="2000" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2000" s="1"/>
-    </row>
-    <row r="2002" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2002" s="1"/>
+    <row r="1997" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1997" s="1"/>
+    </row>
+    <row r="1999" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N1999" s="1"/>
+    </row>
+    <row r="2001" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2001" s="1"/>
     </row>
     <row r="2003" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2003" s="1"/>
     </row>
-    <row r="2007" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2007" s="1"/>
+    <row r="2004" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2004" s="1"/>
     </row>
     <row r="2008" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2008" s="1"/>
@@ -3377,8 +4611,8 @@
     <row r="2009" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2009" s="1"/>
     </row>
-    <row r="2019" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N2019" s="1"/>
+    <row r="2010" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2010" s="1"/>
     </row>
     <row r="2020" spans="3:14" x14ac:dyDescent="0.45">
       <c r="N2020" s="1"/>
@@ -3386,8 +4620,8 @@
     <row r="2021" spans="3:14" x14ac:dyDescent="0.45">
       <c r="N2021" s="1"/>
     </row>
-    <row r="2023" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N2023" s="1"/>
+    <row r="2022" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N2022" s="1"/>
     </row>
     <row r="2024" spans="3:14" x14ac:dyDescent="0.45">
       <c r="N2024" s="1"/>
@@ -3395,125 +4629,125 @@
     <row r="2025" spans="3:14" x14ac:dyDescent="0.45">
       <c r="N2025" s="1"/>
     </row>
-    <row r="2028" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N2028" s="1"/>
+    <row r="2026" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N2026" s="1"/>
     </row>
     <row r="2029" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="C2029" s="1"/>
-    </row>
-    <row r="2031" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N2031" s="1"/>
-    </row>
-    <row r="2034" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2034" s="1"/>
+      <c r="N2029" s="1"/>
+    </row>
+    <row r="2030" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C2030" s="1"/>
+    </row>
+    <row r="2032" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N2032" s="1"/>
     </row>
     <row r="2035" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2035" s="1"/>
     </row>
-    <row r="2037" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2037" s="1"/>
-    </row>
-    <row r="2039" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2039" s="1"/>
-    </row>
-    <row r="2041" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2041" s="1"/>
+    <row r="2036" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2036" s="1"/>
+    </row>
+    <row r="2038" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2038" s="1"/>
+    </row>
+    <row r="2040" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2040" s="1"/>
     </row>
     <row r="2042" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2042" s="1"/>
     </row>
-    <row r="2044" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2044" s="1"/>
-    </row>
-    <row r="2051" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2051" s="1"/>
-    </row>
-    <row r="2057" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2057" s="1"/>
-    </row>
-    <row r="2066" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2066" s="1"/>
-    </row>
-    <row r="2069" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2069" s="1"/>
-    </row>
-    <row r="2071" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2071" s="1"/>
-    </row>
-    <row r="2078" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2078" s="1"/>
-    </row>
-    <row r="2085" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2085" s="1"/>
+    <row r="2043" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2043" s="1"/>
+    </row>
+    <row r="2045" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2045" s="1"/>
+    </row>
+    <row r="2052" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2052" s="1"/>
+    </row>
+    <row r="2058" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2058" s="1"/>
+    </row>
+    <row r="2067" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2067" s="1"/>
+    </row>
+    <row r="2070" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2070" s="1"/>
+    </row>
+    <row r="2072" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2072" s="1"/>
+    </row>
+    <row r="2079" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2079" s="1"/>
     </row>
     <row r="2086" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2086" s="1"/>
     </row>
-    <row r="2090" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2090" s="1"/>
-    </row>
-    <row r="2095" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2095" s="1"/>
+    <row r="2087" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2087" s="1"/>
+    </row>
+    <row r="2091" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2091" s="1"/>
     </row>
     <row r="2096" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2096" s="1"/>
     </row>
-    <row r="2099" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2099" s="1"/>
-    </row>
-    <row r="2102" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2102" s="1"/>
-    </row>
-    <row r="2105" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2105" s="1"/>
-    </row>
-    <row r="2111" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2111" s="1"/>
-    </row>
-    <row r="2123" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2123" s="1"/>
-    </row>
-    <row r="2125" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2125" s="1"/>
+    <row r="2097" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2097" s="1"/>
+    </row>
+    <row r="2100" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2100" s="1"/>
+    </row>
+    <row r="2103" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2103" s="1"/>
+    </row>
+    <row r="2106" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2106" s="1"/>
+    </row>
+    <row r="2112" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2112" s="1"/>
+    </row>
+    <row r="2124" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2124" s="1"/>
     </row>
     <row r="2126" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2126" s="1"/>
     </row>
-    <row r="2128" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2128" s="1"/>
+    <row r="2127" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2127" s="1"/>
     </row>
     <row r="2129" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2129" s="1"/>
     </row>
-    <row r="2138" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2138" s="1"/>
-    </row>
-    <row r="2142" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2142" s="1"/>
-    </row>
-    <row r="2144" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2144" s="1"/>
+    <row r="2130" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2130" s="1"/>
+    </row>
+    <row r="2139" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2139" s="1"/>
+    </row>
+    <row r="2143" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2143" s="1"/>
     </row>
     <row r="2145" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2145" s="1"/>
     </row>
-    <row r="2151" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2151" s="1"/>
-    </row>
-    <row r="2154" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2154" s="1"/>
-    </row>
-    <row r="2159" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2159" s="1"/>
-    </row>
-    <row r="2170" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2170" s="1"/>
-    </row>
-    <row r="2172" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2172" s="1"/>
-    </row>
-    <row r="2175" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2175" s="1"/>
+    <row r="2146" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2146" s="1"/>
+    </row>
+    <row r="2152" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2152" s="1"/>
+    </row>
+    <row r="2155" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2155" s="1"/>
+    </row>
+    <row r="2160" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2160" s="1"/>
+    </row>
+    <row r="2171" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2171" s="1"/>
+    </row>
+    <row r="2173" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2173" s="1"/>
     </row>
     <row r="2176" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2176" s="1"/>
@@ -3521,23 +4755,23 @@
     <row r="2177" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2177" s="1"/>
     </row>
-    <row r="2179" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2179" s="1"/>
-    </row>
-    <row r="2181" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2181" s="1"/>
-    </row>
-    <row r="2186" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2186" s="1"/>
+    <row r="2178" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2178" s="1"/>
+    </row>
+    <row r="2180" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2180" s="1"/>
+    </row>
+    <row r="2182" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2182" s="1"/>
     </row>
     <row r="2187" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2187" s="1"/>
     </row>
-    <row r="2190" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2190" s="1"/>
-    </row>
-    <row r="2197" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2197" s="1"/>
+    <row r="2188" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2188" s="1"/>
+    </row>
+    <row r="2191" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2191" s="1"/>
     </row>
     <row r="2198" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2198" s="1"/>
@@ -3545,23 +4779,23 @@
     <row r="2199" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2199" s="1"/>
     </row>
-    <row r="2210" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2210" s="1"/>
-    </row>
-    <row r="2213" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2213" s="1"/>
-    </row>
-    <row r="2217" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2217" s="1"/>
-    </row>
-    <row r="2219" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2219" s="1"/>
-    </row>
-    <row r="2223" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2223" s="1"/>
-    </row>
-    <row r="2227" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2227" s="1"/>
+    <row r="2200" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2200" s="1"/>
+    </row>
+    <row r="2211" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2211" s="1"/>
+    </row>
+    <row r="2214" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2214" s="1"/>
+    </row>
+    <row r="2218" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2218" s="1"/>
+    </row>
+    <row r="2220" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2220" s="1"/>
+    </row>
+    <row r="2224" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2224" s="1"/>
     </row>
     <row r="2228" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2228" s="1"/>
@@ -3569,20 +4803,20 @@
     <row r="2229" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2229" s="1"/>
     </row>
-    <row r="2231" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2231" s="1"/>
-    </row>
-    <row r="2233" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2233" s="1"/>
+    <row r="2230" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2230" s="1"/>
+    </row>
+    <row r="2232" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2232" s="1"/>
     </row>
     <row r="2234" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2234" s="1"/>
     </row>
-    <row r="2236" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2236" s="1"/>
-    </row>
-    <row r="2243" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2243" s="1"/>
+    <row r="2235" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2235" s="1"/>
+    </row>
+    <row r="2237" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2237" s="1"/>
     </row>
     <row r="2244" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2244" s="1"/>
@@ -3590,17 +4824,17 @@
     <row r="2245" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2245" s="1"/>
     </row>
-    <row r="2247" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2247" s="1"/>
+    <row r="2246" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2246" s="1"/>
     </row>
     <row r="2248" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2248" s="1"/>
     </row>
-    <row r="2250" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2250" s="1"/>
-    </row>
-    <row r="2252" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2252" s="1"/>
+    <row r="2249" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2249" s="1"/>
+    </row>
+    <row r="2251" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2251" s="1"/>
     </row>
     <row r="2253" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2253" s="1"/>
@@ -3611,35 +4845,35 @@
     <row r="2255" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2255" s="1"/>
     </row>
-    <row r="2257" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2257" s="1"/>
-    </row>
-    <row r="2261" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2261" s="1"/>
+    <row r="2256" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2256" s="1"/>
+    </row>
+    <row r="2258" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2258" s="1"/>
     </row>
     <row r="2262" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2262" s="1"/>
     </row>
-    <row r="2269" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2269" s="1"/>
-    </row>
-    <row r="2272" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2272" s="1"/>
-    </row>
-    <row r="2277" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2277" s="1"/>
-    </row>
-    <row r="2279" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2279" s="1"/>
-    </row>
-    <row r="2288" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2288" s="1"/>
-    </row>
-    <row r="2292" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2292" s="1"/>
-    </row>
-    <row r="2294" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2294" s="1"/>
+    <row r="2263" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2263" s="1"/>
+    </row>
+    <row r="2270" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2270" s="1"/>
+    </row>
+    <row r="2273" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2273" s="1"/>
+    </row>
+    <row r="2278" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2278" s="1"/>
+    </row>
+    <row r="2280" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2280" s="1"/>
+    </row>
+    <row r="2289" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2289" s="1"/>
+    </row>
+    <row r="2293" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2293" s="1"/>
     </row>
     <row r="2295" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2295" s="1"/>
@@ -3650,104 +4884,104 @@
     <row r="2297" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2297" s="1"/>
     </row>
-    <row r="2301" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2301" s="1"/>
-    </row>
-    <row r="2303" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2303" s="1"/>
+    <row r="2298" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2298" s="1"/>
+    </row>
+    <row r="2302" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2302" s="1"/>
     </row>
     <row r="2304" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2304" s="1"/>
     </row>
-    <row r="2306" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2306" s="1"/>
-    </row>
-    <row r="2313" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2313" s="1"/>
-    </row>
-    <row r="2322" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2322" s="1"/>
-    </row>
-    <row r="2324" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2324" s="1"/>
-    </row>
-    <row r="2326" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2326" s="1"/>
-    </row>
-    <row r="2329" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2329" s="1"/>
-    </row>
-    <row r="2335" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2335" s="1"/>
-    </row>
-    <row r="2338" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N2338" s="1"/>
-    </row>
-    <row r="2344" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="C2344" s="1"/>
-    </row>
-    <row r="2346" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N2346" s="1"/>
+    <row r="2305" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2305" s="1"/>
+    </row>
+    <row r="2307" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2307" s="1"/>
+    </row>
+    <row r="2314" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2314" s="1"/>
+    </row>
+    <row r="2323" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2323" s="1"/>
+    </row>
+    <row r="2325" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2325" s="1"/>
+    </row>
+    <row r="2327" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2327" s="1"/>
+    </row>
+    <row r="2330" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2330" s="1"/>
+    </row>
+    <row r="2336" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2336" s="1"/>
+    </row>
+    <row r="2339" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N2339" s="1"/>
+    </row>
+    <row r="2345" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C2345" s="1"/>
     </row>
     <row r="2347" spans="3:14" x14ac:dyDescent="0.45">
       <c r="N2347" s="1"/>
     </row>
-    <row r="2353" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N2353" s="1"/>
-    </row>
-    <row r="2355" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N2355" s="1"/>
-    </row>
-    <row r="2359" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N2359" s="1"/>
-    </row>
-    <row r="2361" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N2361" s="1"/>
-    </row>
-    <row r="2363" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="C2363" s="1"/>
+    <row r="2348" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N2348" s="1"/>
+    </row>
+    <row r="2354" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N2354" s="1"/>
+    </row>
+    <row r="2356" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N2356" s="1"/>
+    </row>
+    <row r="2360" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N2360" s="1"/>
+    </row>
+    <row r="2362" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N2362" s="1"/>
     </row>
     <row r="2364" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N2364" s="1"/>
+      <c r="C2364" s="1"/>
     </row>
     <row r="2365" spans="3:14" x14ac:dyDescent="0.45">
       <c r="N2365" s="1"/>
     </row>
-    <row r="2368" spans="3:14" x14ac:dyDescent="0.45">
-      <c r="N2368" s="1"/>
-    </row>
-    <row r="2372" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2372" s="1"/>
+    <row r="2366" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="N2366" s="1"/>
+    </row>
+    <row r="2369" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2369" s="1"/>
     </row>
     <row r="2373" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2373" s="1"/>
     </row>
-    <row r="2375" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2375" s="1"/>
-    </row>
-    <row r="2377" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2377" s="1"/>
+    <row r="2374" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2374" s="1"/>
+    </row>
+    <row r="2376" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2376" s="1"/>
     </row>
     <row r="2378" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2378" s="1"/>
     </row>
-    <row r="2382" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2382" s="1"/>
-    </row>
-    <row r="2389" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2389" s="1"/>
-    </row>
-    <row r="2392" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2392" s="1"/>
-    </row>
-    <row r="2396" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2396" s="1"/>
-    </row>
-    <row r="2398" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2398" s="1"/>
-    </row>
-    <row r="2401" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2401" s="1"/>
+    <row r="2379" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2379" s="1"/>
+    </row>
+    <row r="2383" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2383" s="1"/>
+    </row>
+    <row r="2390" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2390" s="1"/>
+    </row>
+    <row r="2393" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2393" s="1"/>
+    </row>
+    <row r="2397" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2397" s="1"/>
+    </row>
+    <row r="2399" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2399" s="1"/>
     </row>
     <row r="2402" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2402" s="1"/>
@@ -3755,122 +4989,122 @@
     <row r="2403" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2403" s="1"/>
     </row>
-    <row r="2411" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2411" s="1"/>
-    </row>
-    <row r="2422" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2422" s="1"/>
-    </row>
-    <row r="2429" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2429" s="1"/>
+    <row r="2404" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2404" s="1"/>
+    </row>
+    <row r="2412" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2412" s="1"/>
+    </row>
+    <row r="2423" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2423" s="1"/>
     </row>
     <row r="2430" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2430" s="1"/>
     </row>
-    <row r="2440" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2440" s="1"/>
-    </row>
-    <row r="2447" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2447" s="1"/>
+    <row r="2431" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2431" s="1"/>
+    </row>
+    <row r="2441" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2441" s="1"/>
     </row>
     <row r="2448" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2448" s="1"/>
     </row>
-    <row r="2451" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2451" s="1"/>
+    <row r="2449" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2449" s="1"/>
     </row>
     <row r="2452" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2452" s="1"/>
     </row>
-    <row r="2458" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2458" s="1"/>
-    </row>
-    <row r="2463" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2463" s="1"/>
-    </row>
-    <row r="2465" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2465" s="1"/>
-    </row>
-    <row r="2470" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2470" s="1"/>
-    </row>
-    <row r="2473" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2473" s="1"/>
-    </row>
-    <row r="2475" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2475" s="1"/>
-    </row>
-    <row r="2482" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2482" s="1"/>
-    </row>
-    <row r="2486" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2486" s="1"/>
-    </row>
-    <row r="2489" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2489" s="1"/>
-    </row>
-    <row r="2492" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2492" s="1"/>
-    </row>
-    <row r="2499" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2499" s="1"/>
-    </row>
-    <row r="2501" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2501" s="1"/>
-    </row>
-    <row r="2505" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2505" s="1"/>
-    </row>
-    <row r="2514" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2514" s="1"/>
-    </row>
-    <row r="2519" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2519" s="1"/>
-    </row>
-    <row r="2529" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2529" s="1"/>
-    </row>
-    <row r="2535" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2535" s="1"/>
-    </row>
-    <row r="2544" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2544" s="1"/>
-    </row>
-    <row r="2555" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2555" s="1"/>
-    </row>
-    <row r="2561" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2561" s="1"/>
-    </row>
-    <row r="2566" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2566" s="1"/>
-    </row>
-    <row r="2574" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2574" s="1"/>
-    </row>
-    <row r="2576" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2576" s="1"/>
+    <row r="2453" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2453" s="1"/>
+    </row>
+    <row r="2459" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2459" s="1"/>
+    </row>
+    <row r="2464" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2464" s="1"/>
+    </row>
+    <row r="2466" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2466" s="1"/>
+    </row>
+    <row r="2471" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2471" s="1"/>
+    </row>
+    <row r="2474" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2474" s="1"/>
+    </row>
+    <row r="2476" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2476" s="1"/>
+    </row>
+    <row r="2483" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2483" s="1"/>
+    </row>
+    <row r="2487" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2487" s="1"/>
+    </row>
+    <row r="2490" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2490" s="1"/>
+    </row>
+    <row r="2493" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2493" s="1"/>
+    </row>
+    <row r="2500" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2500" s="1"/>
+    </row>
+    <row r="2502" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2502" s="1"/>
+    </row>
+    <row r="2506" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2506" s="1"/>
+    </row>
+    <row r="2515" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2515" s="1"/>
+    </row>
+    <row r="2520" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2520" s="1"/>
+    </row>
+    <row r="2530" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2530" s="1"/>
+    </row>
+    <row r="2536" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2536" s="1"/>
+    </row>
+    <row r="2545" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2545" s="1"/>
+    </row>
+    <row r="2556" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2556" s="1"/>
+    </row>
+    <row r="2562" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2562" s="1"/>
+    </row>
+    <row r="2567" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2567" s="1"/>
+    </row>
+    <row r="2575" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2575" s="1"/>
     </row>
     <row r="2577" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2577" s="1"/>
     </row>
-    <row r="2579" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2579" s="1"/>
-    </row>
-    <row r="2585" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2585" s="1"/>
-    </row>
-    <row r="2591" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2591" s="1"/>
-    </row>
-    <row r="2598" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2598" s="1"/>
-    </row>
-    <row r="2602" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2602" s="1"/>
-    </row>
-    <row r="2604" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2604" s="1"/>
+    <row r="2578" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2578" s="1"/>
+    </row>
+    <row r="2580" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2580" s="1"/>
+    </row>
+    <row r="2586" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2586" s="1"/>
+    </row>
+    <row r="2592" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2592" s="1"/>
+    </row>
+    <row r="2599" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2599" s="1"/>
+    </row>
+    <row r="2603" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2603" s="1"/>
     </row>
     <row r="2605" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2605" s="1"/>
@@ -3878,35 +5112,35 @@
     <row r="2606" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2606" s="1"/>
     </row>
-    <row r="2611" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2611" s="1"/>
-    </row>
-    <row r="2615" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2615" s="1"/>
-    </row>
-    <row r="2617" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2617" s="1"/>
-    </row>
-    <row r="2620" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2620" s="1"/>
-    </row>
-    <row r="2627" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2627" s="1"/>
-    </row>
-    <row r="2629" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2629" s="1"/>
-    </row>
-    <row r="2632" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2632" s="1"/>
+    <row r="2607" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2607" s="1"/>
+    </row>
+    <row r="2612" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2612" s="1"/>
+    </row>
+    <row r="2616" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2616" s="1"/>
+    </row>
+    <row r="2618" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2618" s="1"/>
+    </row>
+    <row r="2621" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2621" s="1"/>
+    </row>
+    <row r="2628" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2628" s="1"/>
+    </row>
+    <row r="2630" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2630" s="1"/>
     </row>
     <row r="2633" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2633" s="1"/>
     </row>
-    <row r="2639" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2639" s="1"/>
-    </row>
-    <row r="2642" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2642" s="1"/>
+    <row r="2634" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2634" s="1"/>
+    </row>
+    <row r="2640" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2640" s="1"/>
     </row>
     <row r="2643" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2643" s="1"/>
@@ -3914,77 +5148,77 @@
     <row r="2644" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2644" s="1"/>
     </row>
-    <row r="2648" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2648" s="1"/>
-    </row>
-    <row r="2650" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2650" s="1"/>
-    </row>
-    <row r="2654" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2654" s="1"/>
+    <row r="2645" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2645" s="1"/>
+    </row>
+    <row r="2649" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2649" s="1"/>
+    </row>
+    <row r="2651" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2651" s="1"/>
     </row>
     <row r="2655" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2655" s="1"/>
     </row>
-    <row r="2662" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2662" s="1"/>
-    </row>
-    <row r="2664" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2664" s="1"/>
+    <row r="2656" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2656" s="1"/>
+    </row>
+    <row r="2663" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2663" s="1"/>
     </row>
     <row r="2665" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2665" s="1"/>
     </row>
-    <row r="2667" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2667" s="1"/>
+    <row r="2666" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2666" s="1"/>
     </row>
     <row r="2668" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2668" s="1"/>
     </row>
-    <row r="2670" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2670" s="1"/>
-    </row>
-    <row r="2679" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2679" s="1"/>
-    </row>
-    <row r="2686" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2686" s="1"/>
-    </row>
-    <row r="2688" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2688" s="1"/>
+    <row r="2669" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2669" s="1"/>
+    </row>
+    <row r="2671" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2671" s="1"/>
+    </row>
+    <row r="2680" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2680" s="1"/>
+    </row>
+    <row r="2687" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2687" s="1"/>
     </row>
     <row r="2689" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2689" s="1"/>
     </row>
-    <row r="2699" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2699" s="1"/>
-    </row>
-    <row r="2704" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2704" s="1"/>
-    </row>
-    <row r="2706" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2706" s="1"/>
+    <row r="2690" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2690" s="1"/>
+    </row>
+    <row r="2700" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2700" s="1"/>
+    </row>
+    <row r="2705" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2705" s="1"/>
     </row>
     <row r="2707" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2707" s="1"/>
     </row>
-    <row r="2709" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2709" s="1"/>
+    <row r="2708" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2708" s="1"/>
     </row>
     <row r="2710" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2710" s="1"/>
     </row>
-    <row r="2713" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2713" s="1"/>
-    </row>
-    <row r="2715" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2715" s="1"/>
-    </row>
-    <row r="2723" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2723" s="1"/>
-    </row>
-    <row r="2732" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2732" s="1"/>
+    <row r="2711" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2711" s="1"/>
+    </row>
+    <row r="2714" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2714" s="1"/>
+    </row>
+    <row r="2716" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2716" s="1"/>
+    </row>
+    <row r="2724" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2724" s="1"/>
     </row>
     <row r="2733" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2733" s="1"/>
@@ -3992,14 +5226,14 @@
     <row r="2734" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2734" s="1"/>
     </row>
-    <row r="2736" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2736" s="1"/>
-    </row>
-    <row r="2739" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2739" s="1"/>
-    </row>
-    <row r="2742" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2742" s="1"/>
+    <row r="2735" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2735" s="1"/>
+    </row>
+    <row r="2737" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2737" s="1"/>
+    </row>
+    <row r="2740" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2740" s="1"/>
     </row>
     <row r="2743" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2743" s="1"/>
@@ -4007,8 +5241,8 @@
     <row r="2744" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2744" s="1"/>
     </row>
-    <row r="2751" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2751" s="1"/>
+    <row r="2745" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2745" s="1"/>
     </row>
     <row r="2752" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2752" s="1"/>
@@ -4016,39 +5250,38 @@
     <row r="2753" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2753" s="1"/>
     </row>
-    <row r="2756" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2756" s="1"/>
-    </row>
-    <row r="2758" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2758" s="1"/>
-    </row>
-    <row r="2763" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2763" s="1"/>
-    </row>
-    <row r="2767" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2767" s="1"/>
-    </row>
-    <row r="2776" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2776" s="1"/>
-    </row>
-    <row r="2778" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2778" s="1"/>
+    <row r="2754" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2754" s="1"/>
+    </row>
+    <row r="2757" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2757" s="1"/>
+    </row>
+    <row r="2759" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2759" s="1"/>
+    </row>
+    <row r="2764" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2764" s="1"/>
+    </row>
+    <row r="2768" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2768" s="1"/>
+    </row>
+    <row r="2777" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2777" s="1"/>
     </row>
     <row r="2779" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2779" s="1"/>
     </row>
-    <row r="2782" spans="14:14" x14ac:dyDescent="0.45">
-      <c r="N2782" s="1"/>
-    </row>
-    <row r="2785" spans="5:14" x14ac:dyDescent="0.45">
-      <c r="N2785" s="1"/>
+    <row r="2780" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2780" s="1"/>
+    </row>
+    <row r="2783" spans="14:14" x14ac:dyDescent="0.45">
+      <c r="N2783" s="1"/>
     </row>
     <row r="2786" spans="5:14" x14ac:dyDescent="0.45">
       <c r="N2786" s="1"/>
     </row>
-    <row r="2788" spans="5:14" x14ac:dyDescent="0.45">
-      <c r="E2788" s="2"/>
-      <c r="N2788" s="1"/>
+    <row r="2787" spans="5:14" x14ac:dyDescent="0.45">
+      <c r="N2787" s="1"/>
     </row>
     <row r="2789" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2789" s="2"/>
@@ -4056,23 +5289,24 @@
     </row>
     <row r="2790" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2790" s="2"/>
+      <c r="N2790" s="1"/>
     </row>
     <row r="2791" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2791" s="2"/>
     </row>
     <row r="2792" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2792" s="2"/>
-      <c r="N2792" s="1"/>
     </row>
     <row r="2793" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2793" s="2"/>
+      <c r="N2793" s="1"/>
     </row>
     <row r="2794" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2794" s="2"/>
-      <c r="N2794" s="1"/>
     </row>
     <row r="2795" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2795" s="2"/>
+      <c r="N2795" s="1"/>
     </row>
     <row r="2796" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2796" s="2"/>
@@ -4091,24 +5325,23 @@
     </row>
     <row r="2801" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2801" s="2"/>
-      <c r="N2801" s="1"/>
     </row>
     <row r="2802" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2802" s="2"/>
+      <c r="N2802" s="1"/>
     </row>
     <row r="2803" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2803" s="2"/>
     </row>
     <row r="2804" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2804" s="2"/>
-      <c r="N2804" s="1"/>
     </row>
     <row r="2805" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2805" s="2"/>
+      <c r="N2805" s="1"/>
     </row>
     <row r="2806" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2806" s="2"/>
-      <c r="N2806" s="1"/>
     </row>
     <row r="2807" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2807" s="2"/>
@@ -4116,17 +5349,17 @@
     </row>
     <row r="2808" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2808" s="2"/>
+      <c r="N2808" s="1"/>
     </row>
     <row r="2809" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2809" s="2"/>
-      <c r="N2809" s="1"/>
     </row>
     <row r="2810" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2810" s="2"/>
+      <c r="N2810" s="1"/>
     </row>
     <row r="2811" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2811" s="2"/>
-      <c r="N2811" s="1"/>
     </row>
     <row r="2812" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2812" s="2"/>
@@ -4138,13 +5371,13 @@
     </row>
     <row r="2814" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2814" s="2"/>
+      <c r="N2814" s="1"/>
     </row>
     <row r="2815" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2815" s="2"/>
     </row>
     <row r="2816" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2816" s="2"/>
-      <c r="N2816" s="1"/>
     </row>
     <row r="2817" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2817" s="2"/>
@@ -4152,6 +5385,7 @@
     </row>
     <row r="2818" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2818" s="2"/>
+      <c r="N2818" s="1"/>
     </row>
     <row r="2819" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2819" s="2"/>
@@ -4164,14 +5398,13 @@
     </row>
     <row r="2822" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2822" s="2"/>
-      <c r="N2822" s="1"/>
     </row>
     <row r="2823" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2823" s="2"/>
+      <c r="N2823" s="1"/>
     </row>
     <row r="2824" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2824" s="2"/>
-      <c r="N2824" s="1"/>
     </row>
     <row r="2825" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2825" s="2"/>
@@ -4179,6 +5412,7 @@
     </row>
     <row r="2826" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2826" s="2"/>
+      <c r="N2826" s="1"/>
     </row>
     <row r="2827" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2827" s="2"/>
@@ -4209,10 +5443,10 @@
     </row>
     <row r="2836" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2836" s="2"/>
-      <c r="N2836" s="1"/>
     </row>
     <row r="2837" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2837" s="2"/>
+      <c r="N2837" s="1"/>
     </row>
     <row r="2838" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2838" s="2"/>
@@ -4234,10 +5468,10 @@
     </row>
     <row r="2844" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2844" s="2"/>
-      <c r="N2844" s="1"/>
     </row>
     <row r="2845" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2845" s="2"/>
+      <c r="N2845" s="1"/>
     </row>
     <row r="2846" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2846" s="2"/>
@@ -4262,10 +5496,10 @@
     </row>
     <row r="2853" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2853" s="2"/>
-      <c r="N2853" s="1"/>
     </row>
     <row r="2854" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2854" s="2"/>
+      <c r="N2854" s="1"/>
     </row>
     <row r="2855" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2855" s="2"/>
@@ -4293,10 +5527,10 @@
     </row>
     <row r="2863" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2863" s="2"/>
-      <c r="N2863" s="1"/>
     </row>
     <row r="2864" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2864" s="2"/>
+      <c r="N2864" s="1"/>
     </row>
     <row r="2865" spans="5:5" x14ac:dyDescent="0.45">
       <c r="E2865" s="2"/>
@@ -4360,17 +5594,17 @@
     </row>
     <row r="2885" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2885" s="2"/>
-      <c r="N2885" s="1"/>
     </row>
     <row r="2886" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2886" s="2"/>
+      <c r="N2886" s="1"/>
     </row>
     <row r="2887" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2887" s="2"/>
-      <c r="N2887" s="1"/>
     </row>
     <row r="2888" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2888" s="2"/>
+      <c r="N2888" s="1"/>
     </row>
     <row r="2889" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2889" s="2"/>
@@ -4386,10 +5620,10 @@
     </row>
     <row r="2893" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2893" s="2"/>
-      <c r="N2893" s="1"/>
     </row>
     <row r="2894" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2894" s="2"/>
+      <c r="N2894" s="1"/>
     </row>
     <row r="2895" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2895" s="2"/>
@@ -4405,17 +5639,17 @@
     </row>
     <row r="2899" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2899" s="2"/>
-      <c r="N2899" s="1"/>
     </row>
     <row r="2900" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2900" s="2"/>
+      <c r="N2900" s="1"/>
     </row>
     <row r="2901" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2901" s="2"/>
-      <c r="N2901" s="1"/>
     </row>
     <row r="2902" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2902" s="2"/>
+      <c r="N2902" s="1"/>
     </row>
     <row r="2903" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2903" s="2"/>
@@ -4437,10 +5671,10 @@
     </row>
     <row r="2909" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2909" s="2"/>
-      <c r="N2909" s="1"/>
     </row>
     <row r="2910" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2910" s="2"/>
+      <c r="N2910" s="1"/>
     </row>
     <row r="2911" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2911" s="2"/>
@@ -4450,10 +5684,10 @@
     </row>
     <row r="2913" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2913" s="2"/>
-      <c r="N2913" s="1"/>
     </row>
     <row r="2914" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2914" s="2"/>
+      <c r="N2914" s="1"/>
     </row>
     <row r="2915" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2915" s="2"/>
@@ -4475,14 +5709,13 @@
     </row>
     <row r="2921" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2921" s="2"/>
-      <c r="N2921" s="1"/>
     </row>
     <row r="2922" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2922" s="2"/>
+      <c r="N2922" s="1"/>
     </row>
     <row r="2923" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2923" s="2"/>
-      <c r="N2923" s="1"/>
     </row>
     <row r="2924" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2924" s="2"/>
@@ -4490,13 +5723,13 @@
     </row>
     <row r="2925" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2925" s="2"/>
+      <c r="N2925" s="1"/>
     </row>
     <row r="2926" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2926" s="2"/>
     </row>
     <row r="2927" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2927" s="2"/>
-      <c r="N2927" s="1"/>
     </row>
     <row r="2928" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2928" s="2"/>
@@ -4504,27 +5737,27 @@
     </row>
     <row r="2929" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2929" s="2"/>
+      <c r="N2929" s="1"/>
     </row>
     <row r="2930" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2930" s="2"/>
-      <c r="N2930" s="1"/>
     </row>
     <row r="2931" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2931" s="2"/>
+      <c r="N2931" s="1"/>
     </row>
     <row r="2932" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2932" s="2"/>
-      <c r="N2932" s="1"/>
     </row>
     <row r="2933" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2933" s="2"/>
+      <c r="N2933" s="1"/>
     </row>
     <row r="2934" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2934" s="2"/>
     </row>
     <row r="2935" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2935" s="2"/>
-      <c r="N2935" s="1"/>
     </row>
     <row r="2936" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2936" s="2"/>
@@ -4532,6 +5765,7 @@
     </row>
     <row r="2937" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2937" s="2"/>
+      <c r="N2937" s="1"/>
     </row>
     <row r="2938" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2938" s="2"/>
@@ -4547,7 +5781,6 @@
     </row>
     <row r="2942" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2942" s="2"/>
-      <c r="N2942" s="1"/>
     </row>
     <row r="2943" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2943" s="2"/>
@@ -4555,6 +5788,7 @@
     </row>
     <row r="2944" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2944" s="2"/>
+      <c r="N2944" s="1"/>
     </row>
     <row r="2945" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2945" s="2"/>
@@ -4570,7 +5804,6 @@
     </row>
     <row r="2949" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2949" s="2"/>
-      <c r="N2949" s="1"/>
     </row>
     <row r="2950" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2950" s="2"/>
@@ -4578,6 +5811,7 @@
     </row>
     <row r="2951" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2951" s="2"/>
+      <c r="N2951" s="1"/>
     </row>
     <row r="2952" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2952" s="2"/>
@@ -4590,7 +5824,6 @@
     </row>
     <row r="2955" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2955" s="2"/>
-      <c r="N2955" s="1"/>
     </row>
     <row r="2956" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2956" s="2"/>
@@ -4598,16 +5831,17 @@
     </row>
     <row r="2957" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2957" s="2"/>
+      <c r="N2957" s="1"/>
     </row>
     <row r="2958" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2958" s="2"/>
     </row>
     <row r="2959" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2959" s="2"/>
-      <c r="N2959" s="1"/>
     </row>
     <row r="2960" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2960" s="2"/>
+      <c r="N2960" s="1"/>
     </row>
     <row r="2961" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2961" s="2"/>
@@ -4623,10 +5857,10 @@
     </row>
     <row r="2965" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2965" s="2"/>
-      <c r="N2965" s="1"/>
     </row>
     <row r="2966" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2966" s="2"/>
+      <c r="N2966" s="1"/>
     </row>
     <row r="2967" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2967" s="2"/>
@@ -4639,7 +5873,6 @@
     </row>
     <row r="2970" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2970" s="2"/>
-      <c r="N2970" s="1"/>
     </row>
     <row r="2971" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2971" s="2"/>
@@ -4647,40 +5880,41 @@
     </row>
     <row r="2972" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2972" s="2"/>
+      <c r="N2972" s="1"/>
     </row>
     <row r="2973" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2973" s="2"/>
     </row>
     <row r="2974" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2974" s="2"/>
-      <c r="N2974" s="1"/>
     </row>
     <row r="2975" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2975" s="2"/>
+      <c r="N2975" s="1"/>
     </row>
     <row r="2976" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2976" s="2"/>
     </row>
     <row r="2977" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2977" s="2"/>
-      <c r="N2977" s="1"/>
     </row>
     <row r="2978" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2978" s="2"/>
+      <c r="N2978" s="1"/>
     </row>
     <row r="2979" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2979" s="2"/>
-      <c r="N2979" s="1"/>
     </row>
     <row r="2980" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2980" s="2"/>
+      <c r="N2980" s="1"/>
     </row>
     <row r="2981" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2981" s="2"/>
-      <c r="N2981" s="1"/>
     </row>
     <row r="2982" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2982" s="2"/>
+      <c r="N2982" s="1"/>
     </row>
     <row r="2983" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2983" s="2"/>
@@ -4690,10 +5924,10 @@
     </row>
     <row r="2985" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2985" s="2"/>
-      <c r="N2985" s="1"/>
     </row>
     <row r="2986" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2986" s="2"/>
+      <c r="N2986" s="1"/>
     </row>
     <row r="2987" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2987" s="2"/>
@@ -4712,7 +5946,6 @@
     </row>
     <row r="2992" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2992" s="2"/>
-      <c r="N2992" s="1"/>
     </row>
     <row r="2993" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2993" s="2"/>
@@ -4720,10 +5953,10 @@
     </row>
     <row r="2994" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2994" s="2"/>
+      <c r="N2994" s="1"/>
     </row>
     <row r="2995" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2995" s="2"/>
-      <c r="N2995" s="1"/>
     </row>
     <row r="2996" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2996" s="2"/>
@@ -4731,6 +5964,7 @@
     </row>
     <row r="2997" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2997" s="2"/>
+      <c r="N2997" s="1"/>
     </row>
     <row r="2998" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E2998" s="2"/>
@@ -4743,7 +5977,6 @@
     </row>
     <row r="3001" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3001" s="2"/>
-      <c r="N3001" s="1"/>
     </row>
     <row r="3002" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3002" s="2"/>
@@ -4751,6 +5984,7 @@
     </row>
     <row r="3003" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3003" s="2"/>
+      <c r="N3003" s="1"/>
     </row>
     <row r="3004" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3004" s="2"/>
@@ -4778,10 +6012,10 @@
     </row>
     <row r="3012" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3012" s="2"/>
-      <c r="N3012" s="1"/>
     </row>
     <row r="3013" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3013" s="2"/>
+      <c r="N3013" s="1"/>
     </row>
     <row r="3014" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3014" s="2"/>
@@ -4794,10 +6028,10 @@
     </row>
     <row r="3017" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3017" s="2"/>
-      <c r="N3017" s="1"/>
     </row>
     <row r="3018" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3018" s="2"/>
+      <c r="N3018" s="1"/>
     </row>
     <row r="3019" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3019" s="2"/>
@@ -4810,27 +6044,27 @@
     </row>
     <row r="3022" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3022" s="2"/>
-      <c r="N3022" s="1"/>
     </row>
     <row r="3023" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3023" s="2"/>
+      <c r="N3023" s="1"/>
     </row>
     <row r="3024" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3024" s="2"/>
     </row>
     <row r="3025" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3025" s="2"/>
-      <c r="N3025" s="1"/>
     </row>
     <row r="3026" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3026" s="2"/>
+      <c r="N3026" s="1"/>
     </row>
     <row r="3027" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3027" s="2"/>
-      <c r="N3027" s="1"/>
     </row>
     <row r="3028" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3028" s="2"/>
+      <c r="N3028" s="1"/>
     </row>
     <row r="3029" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3029" s="2"/>
@@ -4840,10 +6074,10 @@
     </row>
     <row r="3031" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3031" s="2"/>
-      <c r="N3031" s="1"/>
     </row>
     <row r="3032" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3032" s="2"/>
+      <c r="N3032" s="1"/>
     </row>
     <row r="3033" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3033" s="2"/>
@@ -4889,10 +6123,10 @@
     </row>
     <row r="3047" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3047" s="2"/>
-      <c r="N3047" s="1"/>
     </row>
     <row r="3048" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3048" s="2"/>
+      <c r="N3048" s="1"/>
     </row>
     <row r="3049" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3049" s="2"/>
@@ -4908,14 +6142,13 @@
     </row>
     <row r="3053" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3053" s="2"/>
-      <c r="N3053" s="1"/>
     </row>
     <row r="3054" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3054" s="2"/>
+      <c r="N3054" s="1"/>
     </row>
     <row r="3055" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3055" s="2"/>
-      <c r="N3055" s="1"/>
     </row>
     <row r="3056" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3056" s="2"/>
@@ -4923,6 +6156,7 @@
     </row>
     <row r="3057" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3057" s="2"/>
+      <c r="N3057" s="1"/>
     </row>
     <row r="3058" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3058" s="2"/>
@@ -4947,24 +6181,23 @@
     </row>
     <row r="3065" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3065" s="2"/>
-      <c r="N3065" s="1"/>
     </row>
     <row r="3066" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3066" s="2"/>
+      <c r="N3066" s="1"/>
     </row>
     <row r="3067" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3067" s="2"/>
     </row>
     <row r="3068" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3068" s="2"/>
-      <c r="N3068" s="1"/>
     </row>
     <row r="3069" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3069" s="2"/>
+      <c r="N3069" s="1"/>
     </row>
     <row r="3070" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3070" s="2"/>
-      <c r="N3070" s="1"/>
     </row>
     <row r="3071" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3071" s="2"/>
@@ -4972,6 +6205,7 @@
     </row>
     <row r="3072" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3072" s="2"/>
+      <c r="N3072" s="1"/>
     </row>
     <row r="3073" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3073" s="2"/>
@@ -4993,7 +6227,6 @@
     </row>
     <row r="3079" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3079" s="2"/>
-      <c r="N3079" s="1"/>
     </row>
     <row r="3080" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3080" s="2"/>
@@ -5001,16 +6234,17 @@
     </row>
     <row r="3081" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3081" s="2"/>
+      <c r="N3081" s="1"/>
     </row>
     <row r="3082" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3082" s="2"/>
     </row>
     <row r="3083" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3083" s="2"/>
-      <c r="N3083" s="1"/>
     </row>
     <row r="3084" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3084" s="2"/>
+      <c r="N3084" s="1"/>
     </row>
     <row r="3085" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3085" s="2"/>
@@ -5029,14 +6263,13 @@
     </row>
     <row r="3090" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3090" s="2"/>
-      <c r="N3090" s="1"/>
     </row>
     <row r="3091" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3091" s="2"/>
+      <c r="N3091" s="1"/>
     </row>
     <row r="3092" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3092" s="2"/>
-      <c r="N3092" s="1"/>
     </row>
     <row r="3093" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3093" s="2"/>
@@ -5048,6 +6281,7 @@
     </row>
     <row r="3095" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3095" s="2"/>
+      <c r="N3095" s="1"/>
     </row>
     <row r="3096" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3096" s="2"/>
@@ -5081,10 +6315,10 @@
     </row>
     <row r="3106" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3106" s="2"/>
-      <c r="N3106" s="1"/>
     </row>
     <row r="3107" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3107" s="2"/>
+      <c r="N3107" s="1"/>
     </row>
     <row r="3108" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3108" s="2"/>
@@ -5094,10 +6328,10 @@
     </row>
     <row r="3110" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3110" s="2"/>
-      <c r="N3110" s="1"/>
     </row>
     <row r="3111" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3111" s="2"/>
+      <c r="N3111" s="1"/>
     </row>
     <row r="3112" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3112" s="2"/>
@@ -5119,20 +6353,20 @@
     </row>
     <row r="3118" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3118" s="2"/>
-      <c r="N3118" s="1"/>
     </row>
     <row r="3119" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3119" s="2"/>
+      <c r="N3119" s="1"/>
     </row>
     <row r="3120" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3120" s="2"/>
     </row>
     <row r="3121" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3121" s="2"/>
-      <c r="N3121" s="1"/>
     </row>
     <row r="3122" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3122" s="2"/>
+      <c r="N3122" s="1"/>
     </row>
     <row r="3123" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3123" s="2"/>
@@ -5145,27 +6379,27 @@
     </row>
     <row r="3126" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3126" s="2"/>
-      <c r="N3126" s="1"/>
     </row>
     <row r="3127" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3127" s="2"/>
+      <c r="N3127" s="1"/>
     </row>
     <row r="3128" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3128" s="2"/>
-      <c r="N3128" s="1"/>
     </row>
     <row r="3129" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3129" s="2"/>
+      <c r="N3129" s="1"/>
     </row>
     <row r="3130" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3130" s="2"/>
     </row>
     <row r="3131" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3131" s="2"/>
-      <c r="N3131" s="1"/>
     </row>
     <row r="3132" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3132" s="2"/>
+      <c r="N3132" s="1"/>
     </row>
     <row r="3133" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3133" s="2"/>
@@ -5184,7 +6418,6 @@
     </row>
     <row r="3138" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3138" s="2"/>
-      <c r="N3138" s="1"/>
     </row>
     <row r="3139" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3139" s="2"/>
@@ -5196,6 +6429,7 @@
     </row>
     <row r="3141" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3141" s="2"/>
+      <c r="N3141" s="1"/>
     </row>
     <row r="3142" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3142" s="2"/>
@@ -5226,10 +6460,10 @@
     </row>
     <row r="3151" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3151" s="2"/>
-      <c r="N3151" s="1"/>
     </row>
     <row r="3152" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3152" s="2"/>
+      <c r="N3152" s="1"/>
     </row>
     <row r="3153" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3153" s="2"/>
@@ -5251,10 +6485,10 @@
     </row>
     <row r="3159" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3159" s="2"/>
-      <c r="N3159" s="1"/>
     </row>
     <row r="3160" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3160" s="2"/>
+      <c r="N3160" s="1"/>
     </row>
     <row r="3161" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3161" s="2"/>
@@ -5276,17 +6510,17 @@
     </row>
     <row r="3167" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3167" s="2"/>
-      <c r="N3167" s="1"/>
     </row>
     <row r="3168" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3168" s="2"/>
+      <c r="N3168" s="1"/>
     </row>
     <row r="3169" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3169" s="2"/>
-      <c r="N3169" s="1"/>
     </row>
     <row r="3170" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3170" s="2"/>
+      <c r="N3170" s="1"/>
     </row>
     <row r="3171" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3171" s="2"/>
@@ -5305,7 +6539,6 @@
     </row>
     <row r="3176" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3176" s="2"/>
-      <c r="N3176" s="1"/>
     </row>
     <row r="3177" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3177" s="2"/>
@@ -5313,6 +6546,7 @@
     </row>
     <row r="3178" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3178" s="2"/>
+      <c r="N3178" s="1"/>
     </row>
     <row r="3179" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3179" s="2"/>
@@ -5325,20 +6559,20 @@
     </row>
     <row r="3182" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3182" s="2"/>
-      <c r="N3182" s="1"/>
     </row>
     <row r="3183" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3183" s="2"/>
+      <c r="N3183" s="1"/>
     </row>
     <row r="3184" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3184" s="2"/>
     </row>
     <row r="3185" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3185" s="2"/>
-      <c r="N3185" s="1"/>
     </row>
     <row r="3186" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3186" s="2"/>
+      <c r="N3186" s="1"/>
     </row>
     <row r="3187" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3187" s="2"/>
@@ -5354,10 +6588,10 @@
     </row>
     <row r="3191" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3191" s="2"/>
-      <c r="N3191" s="1"/>
     </row>
     <row r="3192" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3192" s="2"/>
+      <c r="N3192" s="1"/>
     </row>
     <row r="3193" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3193" s="2"/>
@@ -5370,10 +6604,10 @@
     </row>
     <row r="3196" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3196" s="2"/>
-      <c r="N3196" s="1"/>
     </row>
     <row r="3197" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3197" s="2"/>
+      <c r="N3197" s="1"/>
     </row>
     <row r="3198" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3198" s="2"/>
@@ -5389,10 +6623,10 @@
     </row>
     <row r="3202" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3202" s="2"/>
-      <c r="N3202" s="1"/>
     </row>
     <row r="3203" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3203" s="2"/>
+      <c r="N3203" s="1"/>
     </row>
     <row r="3204" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3204" s="2"/>
@@ -5408,10 +6642,10 @@
     </row>
     <row r="3208" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3208" s="2"/>
-      <c r="N3208" s="1"/>
     </row>
     <row r="3209" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3209" s="2"/>
+      <c r="N3209" s="1"/>
     </row>
     <row r="3210" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3210" s="2"/>
@@ -5427,10 +6661,10 @@
     </row>
     <row r="3214" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3214" s="2"/>
-      <c r="N3214" s="1"/>
     </row>
     <row r="3215" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3215" s="2"/>
+      <c r="N3215" s="1"/>
     </row>
     <row r="3216" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3216" s="2"/>
@@ -5440,7 +6674,6 @@
     </row>
     <row r="3218" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3218" s="2"/>
-      <c r="N3218" s="1"/>
     </row>
     <row r="3219" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3219" s="2"/>
@@ -5448,6 +6681,7 @@
     </row>
     <row r="3220" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3220" s="2"/>
+      <c r="N3220" s="1"/>
     </row>
     <row r="3221" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3221" s="2"/>
@@ -5460,7 +6694,6 @@
     </row>
     <row r="3224" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3224" s="2"/>
-      <c r="N3224" s="1"/>
     </row>
     <row r="3225" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3225" s="2"/>
@@ -5472,10 +6705,10 @@
     </row>
     <row r="3227" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3227" s="2"/>
+      <c r="N3227" s="1"/>
     </row>
     <row r="3228" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3228" s="2"/>
-      <c r="N3228" s="1"/>
     </row>
     <row r="3229" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3229" s="2"/>
@@ -5487,10 +6720,10 @@
     </row>
     <row r="3231" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3231" s="2"/>
+      <c r="N3231" s="1"/>
     </row>
     <row r="3232" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3232" s="2"/>
-      <c r="N3232" s="1"/>
     </row>
     <row r="3233" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3233" s="2"/>
@@ -5498,6 +6731,7 @@
     </row>
     <row r="3234" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3234" s="2"/>
+      <c r="N3234" s="1"/>
     </row>
     <row r="3235" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3235" s="2"/>
@@ -5522,20 +6756,20 @@
     </row>
     <row r="3242" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3242" s="2"/>
-      <c r="N3242" s="1"/>
     </row>
     <row r="3243" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3243" s="2"/>
+      <c r="N3243" s="1"/>
     </row>
     <row r="3244" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3244" s="2"/>
     </row>
     <row r="3245" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3245" s="2"/>
-      <c r="N3245" s="1"/>
     </row>
     <row r="3246" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3246" s="2"/>
+      <c r="N3246" s="1"/>
     </row>
     <row r="3247" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3247" s="2"/>
@@ -5554,10 +6788,10 @@
     </row>
     <row r="3252" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3252" s="2"/>
-      <c r="N3252" s="1"/>
     </row>
     <row r="3253" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3253" s="2"/>
+      <c r="N3253" s="1"/>
     </row>
     <row r="3254" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3254" s="2"/>
@@ -5582,14 +6816,13 @@
     </row>
     <row r="3261" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3261" s="2"/>
-      <c r="N3261" s="1"/>
     </row>
     <row r="3262" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3262" s="2"/>
+      <c r="N3262" s="1"/>
     </row>
     <row r="3263" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3263" s="2"/>
-      <c r="N3263" s="1"/>
     </row>
     <row r="3264" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3264" s="2"/>
@@ -5597,13 +6830,13 @@
     </row>
     <row r="3265" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3265" s="2"/>
+      <c r="N3265" s="1"/>
     </row>
     <row r="3266" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3266" s="2"/>
     </row>
     <row r="3267" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3267" s="2"/>
-      <c r="N3267" s="1"/>
     </row>
     <row r="3268" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3268" s="2"/>
@@ -5611,6 +6844,7 @@
     </row>
     <row r="3269" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3269" s="2"/>
+      <c r="N3269" s="1"/>
     </row>
     <row r="3270" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3270" s="2"/>
@@ -5626,17 +6860,17 @@
     </row>
     <row r="3274" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3274" s="2"/>
-      <c r="N3274" s="1"/>
     </row>
     <row r="3275" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3275" s="2"/>
+      <c r="N3275" s="1"/>
     </row>
     <row r="3276" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3276" s="2"/>
-      <c r="N3276" s="1"/>
     </row>
     <row r="3277" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3277" s="2"/>
+      <c r="N3277" s="1"/>
     </row>
     <row r="3278" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3278" s="2"/>
@@ -5646,10 +6880,10 @@
     </row>
     <row r="3280" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3280" s="2"/>
-      <c r="N3280" s="1"/>
     </row>
     <row r="3281" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3281" s="2"/>
+      <c r="N3281" s="1"/>
     </row>
     <row r="3282" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3282" s="2"/>
@@ -5674,10 +6908,10 @@
     </row>
     <row r="3289" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3289" s="2"/>
-      <c r="N3289" s="1"/>
     </row>
     <row r="3290" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3290" s="2"/>
+      <c r="N3290" s="1"/>
     </row>
     <row r="3291" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3291" s="2"/>
@@ -5690,10 +6924,10 @@
     </row>
     <row r="3294" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3294" s="2"/>
-      <c r="N3294" s="1"/>
     </row>
     <row r="3295" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3295" s="2"/>
+      <c r="N3295" s="1"/>
     </row>
     <row r="3296" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3296" s="2"/>
@@ -5730,7 +6964,6 @@
     </row>
     <row r="3307" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3307" s="2"/>
-      <c r="N3307" s="1"/>
     </row>
     <row r="3308" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3308" s="2"/>
@@ -5746,6 +6979,7 @@
     </row>
     <row r="3311" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3311" s="2"/>
+      <c r="N3311" s="1"/>
     </row>
     <row r="3312" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3312" s="2"/>
@@ -5761,7 +6995,6 @@
     </row>
     <row r="3316" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3316" s="2"/>
-      <c r="N3316" s="1"/>
     </row>
     <row r="3317" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3317" s="2"/>
@@ -5769,6 +7002,7 @@
     </row>
     <row r="3318" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3318" s="2"/>
+      <c r="N3318" s="1"/>
     </row>
     <row r="3319" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3319" s="2"/>
@@ -5781,20 +7015,20 @@
     </row>
     <row r="3322" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3322" s="2"/>
-      <c r="N3322" s="1"/>
     </row>
     <row r="3323" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3323" s="2"/>
+      <c r="N3323" s="1"/>
     </row>
     <row r="3324" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3324" s="2"/>
     </row>
     <row r="3325" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3325" s="2"/>
-      <c r="N3325" s="1"/>
     </row>
     <row r="3326" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3326" s="2"/>
+      <c r="N3326" s="1"/>
     </row>
     <row r="3327" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3327" s="2"/>
@@ -5804,10 +7038,10 @@
     </row>
     <row r="3329" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3329" s="2"/>
-      <c r="N3329" s="1"/>
     </row>
     <row r="3330" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3330" s="2"/>
+      <c r="N3330" s="1"/>
     </row>
     <row r="3331" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3331" s="2"/>
@@ -5820,17 +7054,17 @@
     </row>
     <row r="3334" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3334" s="2"/>
-      <c r="N3334" s="1"/>
     </row>
     <row r="3335" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3335" s="2"/>
+      <c r="N3335" s="1"/>
     </row>
     <row r="3336" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3336" s="2"/>
-      <c r="N3336" s="1"/>
     </row>
     <row r="3337" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3337" s="2"/>
+      <c r="N3337" s="1"/>
     </row>
     <row r="3338" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3338" s="2"/>
@@ -5840,10 +7074,10 @@
     </row>
     <row r="3340" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3340" s="2"/>
-      <c r="N3340" s="1"/>
     </row>
     <row r="3341" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3341" s="2"/>
+      <c r="N3341" s="1"/>
     </row>
     <row r="3342" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3342" s="2"/>
@@ -5871,10 +7105,10 @@
     </row>
     <row r="3350" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3350" s="2"/>
-      <c r="N3350" s="1"/>
     </row>
     <row r="3351" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3351" s="2"/>
+      <c r="N3351" s="1"/>
     </row>
     <row r="3352" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3352" s="2"/>
@@ -5890,17 +7124,17 @@
     </row>
     <row r="3356" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3356" s="2"/>
-      <c r="N3356" s="1"/>
     </row>
     <row r="3357" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3357" s="2"/>
+      <c r="N3357" s="1"/>
     </row>
     <row r="3358" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3358" s="2"/>
-      <c r="N3358" s="1"/>
     </row>
     <row r="3359" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3359" s="2"/>
+      <c r="N3359" s="1"/>
     </row>
     <row r="3360" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3360" s="2"/>
@@ -5916,10 +7150,10 @@
     </row>
     <row r="3364" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3364" s="2"/>
-      <c r="N3364" s="1"/>
     </row>
     <row r="3365" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3365" s="2"/>
+      <c r="N3365" s="1"/>
     </row>
     <row r="3366" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3366" s="2"/>
@@ -5950,20 +7184,20 @@
     </row>
     <row r="3375" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3375" s="2"/>
-      <c r="N3375" s="1"/>
     </row>
     <row r="3376" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3376" s="2"/>
+      <c r="N3376" s="1"/>
     </row>
     <row r="3377" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3377" s="2"/>
     </row>
     <row r="3378" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3378" s="2"/>
-      <c r="N3378" s="1"/>
     </row>
     <row r="3379" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3379" s="2"/>
+      <c r="N3379" s="1"/>
     </row>
     <row r="3380" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3380" s="2"/>
@@ -5982,37 +7216,37 @@
     </row>
     <row r="3385" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3385" s="2"/>
-      <c r="N3385" s="1"/>
     </row>
     <row r="3386" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3386" s="2"/>
+      <c r="N3386" s="1"/>
     </row>
     <row r="3387" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3387" s="2"/>
     </row>
     <row r="3388" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3388" s="2"/>
-      <c r="N3388" s="1"/>
     </row>
     <row r="3389" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3389" s="2"/>
+      <c r="N3389" s="1"/>
     </row>
     <row r="3390" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3390" s="2"/>
-      <c r="N3390" s="1"/>
     </row>
     <row r="3391" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3391" s="2"/>
+      <c r="N3391" s="1"/>
     </row>
     <row r="3392" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3392" s="2"/>
     </row>
     <row r="3393" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3393" s="2"/>
-      <c r="N3393" s="1"/>
     </row>
     <row r="3394" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3394" s="2"/>
+      <c r="N3394" s="1"/>
     </row>
     <row r="3395" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3395" s="2"/>
@@ -6055,10 +7289,10 @@
     </row>
     <row r="3408" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3408" s="2"/>
-      <c r="N3408" s="1"/>
     </row>
     <row r="3409" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3409" s="2"/>
+      <c r="N3409" s="1"/>
     </row>
     <row r="3410" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3410" s="2"/>
@@ -6071,10 +7305,10 @@
     </row>
     <row r="3413" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3413" s="2"/>
-      <c r="N3413" s="1"/>
     </row>
     <row r="3414" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3414" s="2"/>
+      <c r="N3414" s="1"/>
     </row>
     <row r="3415" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3415" s="2"/>
@@ -6093,10 +7327,10 @@
     </row>
     <row r="3420" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3420" s="2"/>
-      <c r="N3420" s="1"/>
     </row>
     <row r="3421" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3421" s="2"/>
+      <c r="N3421" s="1"/>
     </row>
     <row r="3422" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3422" s="2"/>
@@ -6115,34 +7349,33 @@
     </row>
     <row r="3427" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3427" s="2"/>
-      <c r="N3427" s="1"/>
     </row>
     <row r="3428" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3428" s="2"/>
+      <c r="N3428" s="1"/>
     </row>
     <row r="3429" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3429" s="2"/>
     </row>
     <row r="3430" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3430" s="2"/>
-      <c r="N3430" s="1"/>
     </row>
     <row r="3431" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3431" s="2"/>
+      <c r="N3431" s="1"/>
     </row>
     <row r="3432" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3432" s="2"/>
     </row>
     <row r="3433" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3433" s="2"/>
-      <c r="N3433" s="1"/>
     </row>
     <row r="3434" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3434" s="2"/>
+      <c r="N3434" s="1"/>
     </row>
     <row r="3435" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3435" s="2"/>
-      <c r="N3435" s="1"/>
     </row>
     <row r="3436" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3436" s="2"/>
@@ -6150,13 +7383,14 @@
     </row>
     <row r="3437" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3437" s="2"/>
+      <c r="N3437" s="1"/>
     </row>
     <row r="3438" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3438" s="2"/>
-      <c r="N3438" s="1"/>
     </row>
     <row r="3439" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3439" s="2"/>
+      <c r="N3439" s="1"/>
     </row>
     <row r="3440" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3440" s="2"/>
@@ -6175,10 +7409,10 @@
     </row>
     <row r="3445" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3445" s="2"/>
-      <c r="N3445" s="1"/>
     </row>
     <row r="3446" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3446" s="2"/>
+      <c r="N3446" s="1"/>
     </row>
     <row r="3447" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3447" s="2"/>
@@ -6188,14 +7422,13 @@
     </row>
     <row r="3449" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3449" s="2"/>
-      <c r="N3449" s="1"/>
     </row>
     <row r="3450" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3450" s="2"/>
+      <c r="N3450" s="1"/>
     </row>
     <row r="3451" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3451" s="2"/>
-      <c r="N3451" s="1"/>
     </row>
     <row r="3452" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3452" s="2"/>
@@ -6203,16 +7436,17 @@
     </row>
     <row r="3453" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3453" s="2"/>
+      <c r="N3453" s="1"/>
     </row>
     <row r="3454" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3454" s="2"/>
     </row>
     <row r="3455" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3455" s="2"/>
-      <c r="N3455" s="1"/>
     </row>
     <row r="3456" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3456" s="2"/>
+      <c r="N3456" s="1"/>
     </row>
     <row r="3457" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3457" s="2"/>
@@ -6222,10 +7456,10 @@
     </row>
     <row r="3459" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3459" s="2"/>
-      <c r="N3459" s="1"/>
     </row>
     <row r="3460" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3460" s="2"/>
+      <c r="N3460" s="1"/>
     </row>
     <row r="3461" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3461" s="2"/>
@@ -6241,20 +7475,20 @@
     </row>
     <row r="3465" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3465" s="2"/>
-      <c r="N3465" s="1"/>
     </row>
     <row r="3466" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3466" s="2"/>
+      <c r="N3466" s="1"/>
     </row>
     <row r="3467" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3467" s="2"/>
     </row>
     <row r="3468" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3468" s="2"/>
-      <c r="N3468" s="1"/>
     </row>
     <row r="3469" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3469" s="2"/>
+      <c r="N3469" s="1"/>
     </row>
     <row r="3470" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3470" s="2"/>
@@ -6294,24 +7528,23 @@
     </row>
     <row r="3482" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3482" s="2"/>
-      <c r="N3482" s="1"/>
     </row>
     <row r="3483" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3483" s="2"/>
+      <c r="N3483" s="1"/>
     </row>
     <row r="3484" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3484" s="2"/>
     </row>
     <row r="3485" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3485" s="2"/>
-      <c r="N3485" s="1"/>
     </row>
     <row r="3486" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3486" s="2"/>
+      <c r="N3486" s="1"/>
     </row>
     <row r="3487" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3487" s="2"/>
-      <c r="N3487" s="1"/>
     </row>
     <row r="3488" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3488" s="2"/>
@@ -6319,16 +7552,17 @@
     </row>
     <row r="3489" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3489" s="2"/>
+      <c r="N3489" s="1"/>
     </row>
     <row r="3490" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3490" s="2"/>
     </row>
     <row r="3491" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3491" s="2"/>
-      <c r="N3491" s="1"/>
     </row>
     <row r="3492" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3492" s="2"/>
+      <c r="N3492" s="1"/>
     </row>
     <row r="3493" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3493" s="2"/>
@@ -6353,24 +7587,24 @@
     </row>
     <row r="3500" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3500" s="2"/>
-      <c r="N3500" s="1"/>
     </row>
     <row r="3501" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3501" s="2"/>
+      <c r="N3501" s="1"/>
     </row>
     <row r="3502" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3502" s="2"/>
-      <c r="N3502" s="1"/>
     </row>
     <row r="3503" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3503" s="2"/>
+      <c r="N3503" s="1"/>
     </row>
     <row r="3504" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3504" s="2"/>
-      <c r="N3504" s="1"/>
     </row>
     <row r="3505" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3505" s="2"/>
+      <c r="N3505" s="1"/>
     </row>
     <row r="3506" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3506" s="2"/>
@@ -6386,10 +7620,10 @@
     </row>
     <row r="3510" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3510" s="2"/>
-      <c r="N3510" s="1"/>
     </row>
     <row r="3511" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3511" s="2"/>
+      <c r="N3511" s="1"/>
     </row>
     <row r="3512" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3512" s="2"/>
@@ -6411,10 +7645,10 @@
     </row>
     <row r="3518" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3518" s="2"/>
-      <c r="N3518" s="1"/>
     </row>
     <row r="3519" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3519" s="2"/>
+      <c r="N3519" s="1"/>
     </row>
     <row r="3520" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3520" s="2"/>
@@ -6445,17 +7679,17 @@
     </row>
     <row r="3529" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3529" s="2"/>
-      <c r="N3529" s="1"/>
     </row>
     <row r="3530" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3530" s="2"/>
+      <c r="N3530" s="1"/>
     </row>
     <row r="3531" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3531" s="2"/>
-      <c r="N3531" s="1"/>
     </row>
     <row r="3532" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3532" s="2"/>
+      <c r="N3532" s="1"/>
     </row>
     <row r="3533" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3533" s="2"/>
@@ -6471,37 +7705,37 @@
     </row>
     <row r="3537" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3537" s="2"/>
-      <c r="N3537" s="1"/>
     </row>
     <row r="3538" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3538" s="2"/>
+      <c r="N3538" s="1"/>
     </row>
     <row r="3539" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3539" s="2"/>
     </row>
     <row r="3540" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3540" s="2"/>
-      <c r="N3540" s="1"/>
     </row>
     <row r="3541" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3541" s="2"/>
+      <c r="N3541" s="1"/>
     </row>
     <row r="3542" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3542" s="2"/>
-      <c r="N3542" s="1"/>
     </row>
     <row r="3543" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3543" s="2"/>
+      <c r="N3543" s="1"/>
     </row>
     <row r="3544" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3544" s="2"/>
     </row>
     <row r="3545" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3545" s="2"/>
-      <c r="N3545" s="1"/>
     </row>
     <row r="3546" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3546" s="2"/>
+      <c r="N3546" s="1"/>
     </row>
     <row r="3547" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3547" s="2"/>
@@ -6523,10 +7757,10 @@
     </row>
     <row r="3553" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3553" s="2"/>
-      <c r="N3553" s="1"/>
     </row>
     <row r="3554" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3554" s="2"/>
+      <c r="N3554" s="1"/>
     </row>
     <row r="3555" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3555" s="2"/>
@@ -6542,10 +7776,10 @@
     </row>
     <row r="3559" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3559" s="2"/>
-      <c r="N3559" s="1"/>
     </row>
     <row r="3560" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3560" s="2"/>
+      <c r="N3560" s="1"/>
     </row>
     <row r="3561" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3561" s="2"/>
@@ -6567,10 +7801,10 @@
     </row>
     <row r="3567" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3567" s="2"/>
-      <c r="N3567" s="1"/>
     </row>
     <row r="3568" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3568" s="2"/>
+      <c r="N3568" s="1"/>
     </row>
     <row r="3569" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3569" s="2"/>
@@ -6589,7 +7823,6 @@
     </row>
     <row r="3574" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3574" s="2"/>
-      <c r="N3574" s="1"/>
     </row>
     <row r="3575" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3575" s="2"/>
@@ -6597,6 +7830,7 @@
     </row>
     <row r="3576" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3576" s="2"/>
+      <c r="N3576" s="1"/>
     </row>
     <row r="3577" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3577" s="2"/>
@@ -6618,7 +7852,6 @@
     </row>
     <row r="3583" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3583" s="2"/>
-      <c r="N3583" s="1"/>
     </row>
     <row r="3584" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3584" s="2"/>
@@ -6626,6 +7859,7 @@
     </row>
     <row r="3585" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3585" s="2"/>
+      <c r="N3585" s="1"/>
     </row>
     <row r="3586" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3586" s="2"/>
@@ -6644,10 +7878,10 @@
     </row>
     <row r="3591" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3591" s="2"/>
-      <c r="N3591" s="1"/>
     </row>
     <row r="3592" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3592" s="2"/>
+      <c r="N3592" s="1"/>
     </row>
     <row r="3593" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3593" s="2"/>
@@ -6657,7 +7891,6 @@
     </row>
     <row r="3595" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3595" s="2"/>
-      <c r="N3595" s="1"/>
     </row>
     <row r="3596" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3596" s="2"/>
@@ -6665,6 +7898,7 @@
     </row>
     <row r="3597" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3597" s="2"/>
+      <c r="N3597" s="1"/>
     </row>
     <row r="3598" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3598" s="2"/>
@@ -6680,10 +7914,10 @@
     </row>
     <row r="3602" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3602" s="2"/>
-      <c r="N3602" s="1"/>
     </row>
     <row r="3603" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3603" s="2"/>
+      <c r="N3603" s="1"/>
     </row>
     <row r="3604" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3604" s="2"/>
@@ -6696,10 +7930,10 @@
     </row>
     <row r="3607" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3607" s="2"/>
-      <c r="N3607" s="1"/>
     </row>
     <row r="3608" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3608" s="2"/>
+      <c r="N3608" s="1"/>
     </row>
     <row r="3609" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3609" s="2"/>
@@ -6724,7 +7958,6 @@
     </row>
     <row r="3616" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3616" s="2"/>
-      <c r="N3616" s="1"/>
     </row>
     <row r="3617" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3617" s="2"/>
@@ -6732,13 +7965,14 @@
     </row>
     <row r="3618" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3618" s="2"/>
+      <c r="N3618" s="1"/>
     </row>
     <row r="3619" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3619" s="2"/>
-      <c r="N3619" s="1"/>
     </row>
     <row r="3620" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3620" s="2"/>
+      <c r="N3620" s="1"/>
     </row>
     <row r="3621" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3621" s="2"/>
@@ -6772,10 +8006,10 @@
     </row>
     <row r="3631" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3631" s="2"/>
-      <c r="N3631" s="1"/>
     </row>
     <row r="3632" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3632" s="2"/>
+      <c r="N3632" s="1"/>
     </row>
     <row r="3633" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3633" s="2"/>
@@ -6797,7 +8031,6 @@
     </row>
     <row r="3639" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3639" s="2"/>
-      <c r="N3639" s="1"/>
     </row>
     <row r="3640" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3640" s="2"/>
@@ -6805,23 +8038,24 @@
     </row>
     <row r="3641" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3641" s="2"/>
+      <c r="N3641" s="1"/>
     </row>
     <row r="3642" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3642" s="2"/>
     </row>
     <row r="3643" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3643" s="2"/>
-      <c r="N3643" s="1"/>
     </row>
     <row r="3644" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3644" s="2"/>
+      <c r="N3644" s="1"/>
     </row>
     <row r="3645" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3645" s="2"/>
-      <c r="N3645" s="1"/>
     </row>
     <row r="3646" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3646" s="2"/>
+      <c r="N3646" s="1"/>
     </row>
     <row r="3647" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3647" s="2"/>
@@ -6831,10 +8065,10 @@
     </row>
     <row r="3649" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3649" s="2"/>
-      <c r="N3649" s="1"/>
     </row>
     <row r="3650" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3650" s="2"/>
+      <c r="N3650" s="1"/>
     </row>
     <row r="3651" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3651" s="2"/>
@@ -6844,20 +8078,20 @@
     </row>
     <row r="3653" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3653" s="2"/>
-      <c r="N3653" s="1"/>
     </row>
     <row r="3654" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3654" s="2"/>
+      <c r="N3654" s="1"/>
     </row>
     <row r="3655" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3655" s="2"/>
     </row>
     <row r="3656" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3656" s="2"/>
-      <c r="N3656" s="1"/>
     </row>
     <row r="3657" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3657" s="2"/>
+      <c r="N3657" s="1"/>
     </row>
     <row r="3658" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3658" s="2"/>
@@ -6870,10 +8104,10 @@
     </row>
     <row r="3661" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3661" s="2"/>
-      <c r="N3661" s="1"/>
     </row>
     <row r="3662" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3662" s="2"/>
+      <c r="N3662" s="1"/>
     </row>
     <row r="3663" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3663" s="2"/>
@@ -6922,7 +8156,6 @@
     </row>
     <row r="3678" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3678" s="2"/>
-      <c r="N3678" s="1"/>
     </row>
     <row r="3679" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3679" s="2"/>
@@ -6930,13 +8163,14 @@
     </row>
     <row r="3680" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3680" s="2"/>
+      <c r="N3680" s="1"/>
     </row>
     <row r="3681" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3681" s="2"/>
-      <c r="N3681" s="1"/>
     </row>
     <row r="3682" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3682" s="2"/>
+      <c r="N3682" s="1"/>
     </row>
     <row r="3683" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3683" s="2"/>
@@ -6961,7 +8195,6 @@
     </row>
     <row r="3690" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3690" s="2"/>
-      <c r="N3690" s="1"/>
     </row>
     <row r="3691" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3691" s="2"/>
@@ -6969,6 +8202,7 @@
     </row>
     <row r="3692" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3692" s="2"/>
+      <c r="N3692" s="1"/>
     </row>
     <row r="3693" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3693" s="2"/>
@@ -6987,10 +8221,10 @@
     </row>
     <row r="3698" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3698" s="2"/>
-      <c r="N3698" s="1"/>
     </row>
     <row r="3699" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3699" s="2"/>
+      <c r="N3699" s="1"/>
     </row>
     <row r="3700" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3700" s="2"/>
@@ -7009,10 +8243,10 @@
     </row>
     <row r="3705" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3705" s="2"/>
-      <c r="N3705" s="1"/>
     </row>
     <row r="3706" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3706" s="2"/>
+      <c r="N3706" s="1"/>
     </row>
     <row r="3707" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3707" s="2"/>
@@ -7028,27 +8262,27 @@
     </row>
     <row r="3711" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3711" s="2"/>
-      <c r="N3711" s="1"/>
     </row>
     <row r="3712" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3712" s="2"/>
+      <c r="N3712" s="1"/>
     </row>
     <row r="3713" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3713" s="2"/>
-      <c r="N3713" s="1"/>
     </row>
     <row r="3714" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3714" s="2"/>
+      <c r="N3714" s="1"/>
     </row>
     <row r="3715" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3715" s="2"/>
     </row>
     <row r="3716" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3716" s="2"/>
-      <c r="N3716" s="1"/>
     </row>
     <row r="3717" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3717" s="2"/>
+      <c r="N3717" s="1"/>
     </row>
     <row r="3718" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3718" s="2"/>
@@ -7058,24 +8292,23 @@
     </row>
     <row r="3720" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3720" s="2"/>
-      <c r="N3720" s="1"/>
     </row>
     <row r="3721" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3721" s="2"/>
+      <c r="N3721" s="1"/>
     </row>
     <row r="3722" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3722" s="2"/>
-      <c r="N3722" s="1"/>
     </row>
     <row r="3723" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3723" s="2"/>
+      <c r="N3723" s="1"/>
     </row>
     <row r="3724" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3724" s="2"/>
     </row>
     <row r="3725" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3725" s="2"/>
-      <c r="N3725" s="1"/>
     </row>
     <row r="3726" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3726" s="2"/>
@@ -7083,6 +8316,7 @@
     </row>
     <row r="3727" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3727" s="2"/>
+      <c r="N3727" s="1"/>
     </row>
     <row r="3728" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3728" s="2"/>
@@ -7095,17 +8329,16 @@
     </row>
     <row r="3731" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3731" s="2"/>
-      <c r="N3731" s="1"/>
     </row>
     <row r="3732" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3732" s="2"/>
+      <c r="N3732" s="1"/>
     </row>
     <row r="3733" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3733" s="2"/>
     </row>
     <row r="3734" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3734" s="2"/>
-      <c r="N3734" s="1"/>
     </row>
     <row r="3735" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3735" s="2"/>
@@ -7113,6 +8346,7 @@
     </row>
     <row r="3736" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3736" s="2"/>
+      <c r="N3736" s="1"/>
     </row>
     <row r="3737" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3737" s="2"/>
@@ -7143,10 +8377,10 @@
     </row>
     <row r="3746" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3746" s="2"/>
-      <c r="N3746" s="1"/>
     </row>
     <row r="3747" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3747" s="2"/>
+      <c r="N3747" s="1"/>
     </row>
     <row r="3748" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3748" s="2"/>
@@ -7189,10 +8423,10 @@
     </row>
     <row r="3761" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3761" s="2"/>
-      <c r="N3761" s="1"/>
     </row>
     <row r="3762" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3762" s="2"/>
+      <c r="N3762" s="1"/>
     </row>
     <row r="3763" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3763" s="2"/>
@@ -7205,17 +8439,17 @@
     </row>
     <row r="3766" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3766" s="2"/>
-      <c r="N3766" s="1"/>
     </row>
     <row r="3767" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3767" s="2"/>
+      <c r="N3767" s="1"/>
     </row>
     <row r="3768" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3768" s="2"/>
-      <c r="N3768" s="1"/>
     </row>
     <row r="3769" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3769" s="2"/>
+      <c r="N3769" s="1"/>
     </row>
     <row r="3770" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3770" s="2"/>
@@ -7228,10 +8462,10 @@
     </row>
     <row r="3773" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3773" s="2"/>
-      <c r="N3773" s="1"/>
     </row>
     <row r="3774" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3774" s="2"/>
+      <c r="N3774" s="1"/>
     </row>
     <row r="3775" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3775" s="2"/>
@@ -7241,10 +8475,10 @@
     </row>
     <row r="3777" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3777" s="2"/>
-      <c r="N3777" s="1"/>
     </row>
     <row r="3778" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3778" s="2"/>
+      <c r="N3778" s="1"/>
     </row>
     <row r="3779" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3779" s="2"/>
@@ -7272,10 +8506,10 @@
     </row>
     <row r="3787" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3787" s="2"/>
-      <c r="N3787" s="1"/>
     </row>
     <row r="3788" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3788" s="2"/>
+      <c r="N3788" s="1"/>
     </row>
     <row r="3789" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3789" s="2"/>
@@ -7285,10 +8519,10 @@
     </row>
     <row r="3791" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3791" s="2"/>
-      <c r="N3791" s="1"/>
     </row>
     <row r="3792" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3792" s="2"/>
+      <c r="N3792" s="1"/>
     </row>
     <row r="3793" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3793" s="2"/>
@@ -7310,10 +8544,10 @@
     </row>
     <row r="3799" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3799" s="2"/>
-      <c r="N3799" s="1"/>
     </row>
     <row r="3800" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3800" s="2"/>
+      <c r="N3800" s="1"/>
     </row>
     <row r="3801" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3801" s="2"/>
@@ -7323,10 +8557,10 @@
     </row>
     <row r="3803" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3803" s="2"/>
-      <c r="N3803" s="1"/>
     </row>
     <row r="3804" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3804" s="2"/>
+      <c r="N3804" s="1"/>
     </row>
     <row r="3805" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3805" s="2"/>
@@ -7339,10 +8573,10 @@
     </row>
     <row r="3808" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3808" s="2"/>
-      <c r="N3808" s="1"/>
     </row>
     <row r="3809" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3809" s="2"/>
+      <c r="N3809" s="1"/>
     </row>
     <row r="3810" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3810" s="2"/>
@@ -7361,7 +8595,6 @@
     </row>
     <row r="3815" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3815" s="2"/>
-      <c r="N3815" s="1"/>
     </row>
     <row r="3816" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3816" s="2"/>
@@ -7369,6 +8602,7 @@
     </row>
     <row r="3817" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3817" s="2"/>
+      <c r="N3817" s="1"/>
     </row>
     <row r="3818" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3818" s="2"/>
@@ -7378,10 +8612,10 @@
     </row>
     <row r="3820" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3820" s="2"/>
-      <c r="N3820" s="1"/>
     </row>
     <row r="3821" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3821" s="2"/>
+      <c r="N3821" s="1"/>
     </row>
     <row r="3822" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3822" s="2"/>
@@ -7394,14 +8628,13 @@
     </row>
     <row r="3825" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3825" s="2"/>
-      <c r="N3825" s="1"/>
     </row>
     <row r="3826" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3826" s="2"/>
+      <c r="N3826" s="1"/>
     </row>
     <row r="3827" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3827" s="2"/>
-      <c r="N3827" s="1"/>
     </row>
     <row r="3828" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3828" s="2"/>
@@ -7413,6 +8646,7 @@
     </row>
     <row r="3830" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3830" s="2"/>
+      <c r="N3830" s="1"/>
     </row>
     <row r="3831" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3831" s="2"/>
@@ -7422,7 +8656,6 @@
     </row>
     <row r="3833" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3833" s="2"/>
-      <c r="N3833" s="1"/>
     </row>
     <row r="3834" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3834" s="2"/>
@@ -7430,13 +8663,14 @@
     </row>
     <row r="3835" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3835" s="2"/>
+      <c r="N3835" s="1"/>
     </row>
     <row r="3836" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3836" s="2"/>
-      <c r="N3836" s="1"/>
     </row>
     <row r="3837" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3837" s="2"/>
+      <c r="N3837" s="1"/>
     </row>
     <row r="3838" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3838" s="2"/>
@@ -7449,10 +8683,10 @@
     </row>
     <row r="3841" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3841" s="2"/>
-      <c r="N3841" s="1"/>
     </row>
     <row r="3842" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3842" s="2"/>
+      <c r="N3842" s="1"/>
     </row>
     <row r="3843" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3843" s="2"/>
@@ -7525,10 +8759,10 @@
     </row>
     <row r="3866" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3866" s="2"/>
-      <c r="N3866" s="1"/>
     </row>
     <row r="3867" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3867" s="2"/>
+      <c r="N3867" s="1"/>
     </row>
     <row r="3868" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3868" s="2"/>
@@ -7550,7 +8784,6 @@
     </row>
     <row r="3874" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3874" s="2"/>
-      <c r="N3874" s="1"/>
     </row>
     <row r="3875" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3875" s="2"/>
@@ -7566,6 +8799,7 @@
     </row>
     <row r="3878" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3878" s="2"/>
+      <c r="N3878" s="1"/>
     </row>
     <row r="3879" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3879" s="2"/>
@@ -7587,7 +8821,6 @@
     </row>
     <row r="3885" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3885" s="2"/>
-      <c r="N3885" s="1"/>
     </row>
     <row r="3886" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3886" s="2"/>
@@ -7599,6 +8832,7 @@
     </row>
     <row r="3888" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3888" s="2"/>
+      <c r="N3888" s="1"/>
     </row>
     <row r="3889" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3889" s="2"/>
@@ -7614,10 +8848,10 @@
     </row>
     <row r="3893" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3893" s="2"/>
-      <c r="N3893" s="1"/>
     </row>
     <row r="3894" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3894" s="2"/>
+      <c r="N3894" s="1"/>
     </row>
     <row r="3895" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3895" s="2"/>
@@ -7627,20 +8861,20 @@
     </row>
     <row r="3897" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3897" s="2"/>
-      <c r="N3897" s="1"/>
     </row>
     <row r="3898" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3898" s="2"/>
+      <c r="N3898" s="1"/>
     </row>
     <row r="3899" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3899" s="2"/>
     </row>
     <row r="3900" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3900" s="2"/>
-      <c r="N3900" s="1"/>
     </row>
     <row r="3901" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3901" s="2"/>
+      <c r="N3901" s="1"/>
     </row>
     <row r="3902" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3902" s="2"/>
@@ -7653,10 +8887,10 @@
     </row>
     <row r="3905" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3905" s="2"/>
-      <c r="N3905" s="1"/>
     </row>
     <row r="3906" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3906" s="2"/>
+      <c r="N3906" s="1"/>
     </row>
     <row r="3907" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3907" s="2"/>
@@ -7669,10 +8903,10 @@
     </row>
     <row r="3910" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3910" s="2"/>
-      <c r="N3910" s="1"/>
     </row>
     <row r="3911" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3911" s="2"/>
+      <c r="N3911" s="1"/>
     </row>
     <row r="3912" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3912" s="2"/>
@@ -7691,7 +8925,6 @@
     </row>
     <row r="3917" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3917" s="2"/>
-      <c r="N3917" s="1"/>
     </row>
     <row r="3918" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3918" s="2"/>
@@ -7703,16 +8936,17 @@
     </row>
     <row r="3920" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3920" s="2"/>
+      <c r="N3920" s="1"/>
     </row>
     <row r="3921" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3921" s="2"/>
     </row>
     <row r="3922" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3922" s="2"/>
-      <c r="N3922" s="1"/>
     </row>
     <row r="3923" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3923" s="2"/>
+      <c r="N3923" s="1"/>
     </row>
     <row r="3924" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3924" s="2"/>
@@ -7734,7 +8968,6 @@
     </row>
     <row r="3930" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3930" s="2"/>
-      <c r="N3930" s="1"/>
     </row>
     <row r="3931" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3931" s="2"/>
@@ -7742,6 +8975,7 @@
     </row>
     <row r="3932" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3932" s="2"/>
+      <c r="N3932" s="1"/>
     </row>
     <row r="3933" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3933" s="2"/>
@@ -7769,7 +9003,6 @@
     </row>
     <row r="3941" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3941" s="2"/>
-      <c r="N3941" s="1"/>
     </row>
     <row r="3942" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3942" s="2"/>
@@ -7777,10 +9010,10 @@
     </row>
     <row r="3943" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3943" s="2"/>
+      <c r="N3943" s="1"/>
     </row>
     <row r="3944" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3944" s="2"/>
-      <c r="N3944" s="1"/>
     </row>
     <row r="3945" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3945" s="2"/>
@@ -7792,16 +9025,17 @@
     </row>
     <row r="3947" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3947" s="2"/>
+      <c r="N3947" s="1"/>
     </row>
     <row r="3948" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3948" s="2"/>
     </row>
     <row r="3949" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3949" s="2"/>
-      <c r="N3949" s="1"/>
     </row>
     <row r="3950" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3950" s="2"/>
+      <c r="N3950" s="1"/>
     </row>
     <row r="3951" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3951" s="2"/>
@@ -7811,10 +9045,10 @@
     </row>
     <row r="3953" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3953" s="2"/>
-      <c r="N3953" s="1"/>
     </row>
     <row r="3954" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3954" s="2"/>
+      <c r="N3954" s="1"/>
     </row>
     <row r="3955" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3955" s="2"/>
@@ -7824,7 +9058,6 @@
     </row>
     <row r="3957" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3957" s="2"/>
-      <c r="N3957" s="1"/>
     </row>
     <row r="3958" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3958" s="2"/>
@@ -7832,6 +9065,7 @@
     </row>
     <row r="3959" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3959" s="2"/>
+      <c r="N3959" s="1"/>
     </row>
     <row r="3960" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3960" s="2"/>
@@ -7841,10 +9075,10 @@
     </row>
     <row r="3962" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3962" s="2"/>
-      <c r="N3962" s="1"/>
     </row>
     <row r="3963" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3963" s="2"/>
+      <c r="N3963" s="1"/>
     </row>
     <row r="3964" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3964" s="2"/>
@@ -7863,10 +9097,10 @@
     </row>
     <row r="3969" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3969" s="2"/>
-      <c r="N3969" s="1"/>
     </row>
     <row r="3970" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3970" s="2"/>
+      <c r="N3970" s="1"/>
     </row>
     <row r="3971" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3971" s="2"/>
@@ -7879,10 +9113,10 @@
     </row>
     <row r="3974" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3974" s="2"/>
-      <c r="N3974" s="1"/>
     </row>
     <row r="3975" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3975" s="2"/>
+      <c r="N3975" s="1"/>
     </row>
     <row r="3976" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3976" s="2"/>
@@ -7916,10 +9150,10 @@
     </row>
     <row r="3986" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3986" s="2"/>
-      <c r="N3986" s="1"/>
     </row>
     <row r="3987" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3987" s="2"/>
+      <c r="N3987" s="1"/>
     </row>
     <row r="3988" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3988" s="2"/>
@@ -7935,14 +9169,13 @@
     </row>
     <row r="3992" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3992" s="2"/>
-      <c r="N3992" s="1"/>
     </row>
     <row r="3993" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3993" s="2"/>
+      <c r="N3993" s="1"/>
     </row>
     <row r="3994" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3994" s="2"/>
-      <c r="N3994" s="1"/>
     </row>
     <row r="3995" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3995" s="2"/>
@@ -7950,6 +9183,7 @@
     </row>
     <row r="3996" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3996" s="2"/>
+      <c r="N3996" s="1"/>
     </row>
     <row r="3997" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E3997" s="2"/>
@@ -7971,7 +9205,6 @@
     </row>
     <row r="4003" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4003" s="2"/>
-      <c r="N4003" s="1"/>
     </row>
     <row r="4004" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4004" s="2"/>
@@ -7983,6 +9216,7 @@
     </row>
     <row r="4006" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4006" s="2"/>
+      <c r="N4006" s="1"/>
     </row>
     <row r="4007" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4007" s="2"/>
@@ -8001,7 +9235,6 @@
     </row>
     <row r="4012" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4012" s="2"/>
-      <c r="N4012" s="1"/>
     </row>
     <row r="4013" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4013" s="2"/>
@@ -8009,6 +9242,7 @@
     </row>
     <row r="4014" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4014" s="2"/>
+      <c r="N4014" s="1"/>
     </row>
     <row r="4015" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4015" s="2"/>
@@ -8042,21 +9276,20 @@
     </row>
     <row r="4025" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4025" s="2"/>
-      <c r="N4025" s="1"/>
     </row>
     <row r="4026" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4026" s="2"/>
+      <c r="N4026" s="1"/>
     </row>
     <row r="4027" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4027" s="2"/>
-      <c r="N4027" s="1"/>
     </row>
     <row r="4028" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4028" s="2"/>
+      <c r="N4028" s="1"/>
     </row>
     <row r="4029" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4029" s="2"/>
-      <c r="N4029" s="1"/>
     </row>
     <row r="4030" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4030" s="2"/>
@@ -8064,6 +9297,7 @@
     </row>
     <row r="4031" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4031" s="2"/>
+      <c r="N4031" s="1"/>
     </row>
     <row r="4032" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4032" s="2"/>
@@ -8088,7 +9322,6 @@
     </row>
     <row r="4039" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4039" s="2"/>
-      <c r="N4039" s="1"/>
     </row>
     <row r="4040" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4040" s="2"/>
@@ -8096,13 +9329,14 @@
     </row>
     <row r="4041" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4041" s="2"/>
+      <c r="N4041" s="1"/>
     </row>
     <row r="4042" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4042" s="2"/>
-      <c r="N4042" s="1"/>
     </row>
     <row r="4043" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4043" s="2"/>
+      <c r="N4043" s="1"/>
     </row>
     <row r="4044" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4044" s="2"/>
@@ -8112,17 +9346,17 @@
     </row>
     <row r="4046" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4046" s="2"/>
-      <c r="N4046" s="1"/>
     </row>
     <row r="4047" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4047" s="2"/>
+      <c r="N4047" s="1"/>
     </row>
     <row r="4048" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4048" s="2"/>
-      <c r="N4048" s="1"/>
     </row>
     <row r="4049" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4049" s="2"/>
+      <c r="N4049" s="1"/>
     </row>
     <row r="4050" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4050" s="2"/>
@@ -8138,27 +9372,27 @@
     </row>
     <row r="4054" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4054" s="2"/>
-      <c r="N4054" s="1"/>
     </row>
     <row r="4055" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4055" s="2"/>
+      <c r="N4055" s="1"/>
     </row>
     <row r="4056" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4056" s="2"/>
     </row>
     <row r="4057" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4057" s="2"/>
-      <c r="N4057" s="1"/>
     </row>
     <row r="4058" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4058" s="2"/>
+      <c r="N4058" s="1"/>
     </row>
     <row r="4059" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4059" s="2"/>
-      <c r="N4059" s="1"/>
     </row>
     <row r="4060" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4060" s="2"/>
+      <c r="N4060" s="1"/>
     </row>
     <row r="4061" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4061" s="2"/>
@@ -8177,7 +9411,6 @@
     </row>
     <row r="4066" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4066" s="2"/>
-      <c r="N4066" s="1"/>
     </row>
     <row r="4067" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4067" s="2"/>
@@ -8185,26 +9418,27 @@
     </row>
     <row r="4068" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4068" s="2"/>
+      <c r="N4068" s="1"/>
     </row>
     <row r="4069" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4069" s="2"/>
     </row>
     <row r="4070" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4070" s="2"/>
-      <c r="N4070" s="1"/>
     </row>
     <row r="4071" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4071" s="2"/>
+      <c r="N4071" s="1"/>
     </row>
     <row r="4072" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4072" s="2"/>
     </row>
     <row r="4073" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4073" s="2"/>
-      <c r="N4073" s="1"/>
     </row>
     <row r="4074" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4074" s="2"/>
+      <c r="N4074" s="1"/>
     </row>
     <row r="4075" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4075" s="2"/>
@@ -8247,10 +9481,10 @@
     </row>
     <row r="4088" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4088" s="2"/>
-      <c r="N4088" s="1"/>
     </row>
     <row r="4089" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4089" s="2"/>
+      <c r="N4089" s="1"/>
     </row>
     <row r="4090" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4090" s="2"/>
@@ -8260,14 +9494,13 @@
     </row>
     <row r="4092" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4092" s="2"/>
-      <c r="N4092" s="1"/>
     </row>
     <row r="4093" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4093" s="2"/>
+      <c r="N4093" s="1"/>
     </row>
     <row r="4094" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4094" s="2"/>
-      <c r="N4094" s="1"/>
     </row>
     <row r="4095" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4095" s="2"/>
@@ -8275,6 +9508,7 @@
     </row>
     <row r="4096" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4096" s="2"/>
+      <c r="N4096" s="1"/>
     </row>
     <row r="4097" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4097" s="2"/>
@@ -8317,7 +9551,6 @@
     </row>
     <row r="4110" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4110" s="2"/>
-      <c r="N4110" s="1"/>
     </row>
     <row r="4111" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4111" s="2"/>
@@ -8325,10 +9558,10 @@
     </row>
     <row r="4112" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4112" s="2"/>
+      <c r="N4112" s="1"/>
     </row>
     <row r="4113" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4113" s="2"/>
-      <c r="N4113" s="1"/>
     </row>
     <row r="4114" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4114" s="2"/>
@@ -8340,16 +9573,17 @@
     </row>
     <row r="4116" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4116" s="2"/>
+      <c r="N4116" s="1"/>
     </row>
     <row r="4117" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4117" s="2"/>
     </row>
     <row r="4118" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4118" s="2"/>
-      <c r="N4118" s="1"/>
     </row>
     <row r="4119" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4119" s="2"/>
+      <c r="N4119" s="1"/>
     </row>
     <row r="4120" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4120" s="2"/>
@@ -8368,7 +9602,6 @@
     </row>
     <row r="4125" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4125" s="2"/>
-      <c r="N4125" s="1"/>
     </row>
     <row r="4126" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4126" s="2"/>
@@ -8376,6 +9609,7 @@
     </row>
     <row r="4127" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4127" s="2"/>
+      <c r="N4127" s="1"/>
     </row>
     <row r="4128" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4128" s="2"/>
@@ -8400,10 +9634,10 @@
     </row>
     <row r="4135" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4135" s="2"/>
-      <c r="N4135" s="1"/>
     </row>
     <row r="4136" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4136" s="2"/>
+      <c r="N4136" s="1"/>
     </row>
     <row r="4137" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4137" s="2"/>
@@ -8422,17 +9656,16 @@
     </row>
     <row r="4142" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4142" s="2"/>
-      <c r="N4142" s="1"/>
     </row>
     <row r="4143" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4143" s="2"/>
+      <c r="N4143" s="1"/>
     </row>
     <row r="4144" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4144" s="2"/>
     </row>
     <row r="4145" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4145" s="2"/>
-      <c r="N4145" s="1"/>
     </row>
     <row r="4146" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4146" s="2"/>
@@ -8440,6 +9673,7 @@
     </row>
     <row r="4147" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4147" s="2"/>
+      <c r="N4147" s="1"/>
     </row>
     <row r="4148" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4148" s="2"/>
@@ -8452,10 +9686,10 @@
     </row>
     <row r="4151" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4151" s="2"/>
-      <c r="N4151" s="1"/>
     </row>
     <row r="4152" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4152" s="2"/>
+      <c r="N4152" s="1"/>
     </row>
     <row r="4153" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4153" s="2"/>
@@ -8468,20 +9702,20 @@
     </row>
     <row r="4156" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4156" s="2"/>
-      <c r="N4156" s="1"/>
     </row>
     <row r="4157" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4157" s="2"/>
+      <c r="N4157" s="1"/>
     </row>
     <row r="4158" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4158" s="2"/>
     </row>
     <row r="4159" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4159" s="2"/>
-      <c r="N4159" s="1"/>
     </row>
     <row r="4160" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4160" s="2"/>
+      <c r="N4160" s="1"/>
     </row>
     <row r="4161" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4161" s="2"/>
@@ -8494,10 +9728,10 @@
     </row>
     <row r="4164" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4164" s="2"/>
-      <c r="N4164" s="1"/>
     </row>
     <row r="4165" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4165" s="2"/>
+      <c r="N4165" s="1"/>
     </row>
     <row r="4166" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4166" s="2"/>
@@ -8513,7 +9747,6 @@
     </row>
     <row r="4170" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4170" s="2"/>
-      <c r="N4170" s="1"/>
     </row>
     <row r="4171" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4171" s="2"/>
@@ -8525,6 +9758,7 @@
     </row>
     <row r="4173" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4173" s="2"/>
+      <c r="N4173" s="1"/>
     </row>
     <row r="4174" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4174" s="2"/>
@@ -8537,7 +9771,6 @@
     </row>
     <row r="4177" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4177" s="2"/>
-      <c r="N4177" s="1"/>
     </row>
     <row r="4178" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4178" s="2"/>
@@ -8545,6 +9778,7 @@
     </row>
     <row r="4179" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4179" s="2"/>
+      <c r="N4179" s="1"/>
     </row>
     <row r="4180" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4180" s="2"/>
@@ -8587,24 +9821,24 @@
     </row>
     <row r="4193" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4193" s="2"/>
-      <c r="N4193" s="1"/>
     </row>
     <row r="4194" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4194" s="2"/>
+      <c r="N4194" s="1"/>
     </row>
     <row r="4195" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4195" s="2"/>
-      <c r="N4195" s="1"/>
     </row>
     <row r="4196" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4196" s="2"/>
+      <c r="N4196" s="1"/>
     </row>
     <row r="4197" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4197" s="2"/>
-      <c r="N4197" s="1"/>
     </row>
     <row r="4198" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4198" s="2"/>
+      <c r="N4198" s="1"/>
     </row>
     <row r="4199" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4199" s="2"/>
@@ -8629,7 +9863,6 @@
     </row>
     <row r="4206" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4206" s="2"/>
-      <c r="N4206" s="1"/>
     </row>
     <row r="4207" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4207" s="2"/>
@@ -8637,6 +9870,7 @@
     </row>
     <row r="4208" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4208" s="2"/>
+      <c r="N4208" s="1"/>
     </row>
     <row r="4209" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4209" s="2"/>
@@ -8646,10 +9880,10 @@
     </row>
     <row r="4211" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4211" s="2"/>
-      <c r="N4211" s="1"/>
     </row>
     <row r="4212" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4212" s="2"/>
+      <c r="N4212" s="1"/>
     </row>
     <row r="4213" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4213" s="2"/>
@@ -8668,7 +9902,6 @@
     </row>
     <row r="4218" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4218" s="2"/>
-      <c r="N4218" s="1"/>
     </row>
     <row r="4219" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4219" s="2"/>
@@ -8676,23 +9909,24 @@
     </row>
     <row r="4220" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4220" s="2"/>
+      <c r="N4220" s="1"/>
     </row>
     <row r="4221" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4221" s="2"/>
-      <c r="N4221" s="1"/>
     </row>
     <row r="4222" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4222" s="2"/>
+      <c r="N4222" s="1"/>
     </row>
     <row r="4223" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4223" s="2"/>
     </row>
     <row r="4224" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4224" s="2"/>
-      <c r="N4224" s="1"/>
     </row>
     <row r="4225" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4225" s="2"/>
+      <c r="N4225" s="1"/>
     </row>
     <row r="4226" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4226" s="2"/>
@@ -8711,17 +9945,17 @@
     </row>
     <row r="4231" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4231" s="2"/>
-      <c r="N4231" s="1"/>
     </row>
     <row r="4232" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4232" s="2"/>
+      <c r="N4232" s="1"/>
     </row>
     <row r="4233" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4233" s="2"/>
-      <c r="N4233" s="1"/>
     </row>
     <row r="4234" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4234" s="2"/>
+      <c r="N4234" s="1"/>
     </row>
     <row r="4235" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4235" s="2"/>
@@ -8737,24 +9971,23 @@
     </row>
     <row r="4239" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4239" s="2"/>
-      <c r="N4239" s="1"/>
     </row>
     <row r="4240" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4240" s="2"/>
+      <c r="N4240" s="1"/>
     </row>
     <row r="4241" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4241" s="2"/>
-      <c r="N4241" s="1"/>
     </row>
     <row r="4242" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4242" s="2"/>
+      <c r="N4242" s="1"/>
     </row>
     <row r="4243" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4243" s="2"/>
     </row>
     <row r="4244" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4244" s="2"/>
-      <c r="N4244" s="1"/>
     </row>
     <row r="4245" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4245" s="2"/>
@@ -8762,6 +9995,7 @@
     </row>
     <row r="4246" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4246" s="2"/>
+      <c r="N4246" s="1"/>
     </row>
     <row r="4247" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4247" s="2"/>
@@ -8777,7 +10011,6 @@
     </row>
     <row r="4251" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4251" s="2"/>
-      <c r="N4251" s="1"/>
     </row>
     <row r="4252" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4252" s="2"/>
@@ -8789,23 +10022,24 @@
     </row>
     <row r="4254" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4254" s="2"/>
+      <c r="N4254" s="1"/>
     </row>
     <row r="4255" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4255" s="2"/>
     </row>
     <row r="4256" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4256" s="2"/>
-      <c r="N4256" s="1"/>
     </row>
     <row r="4257" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4257" s="2"/>
+      <c r="N4257" s="1"/>
     </row>
     <row r="4258" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4258" s="2"/>
-      <c r="N4258" s="1"/>
     </row>
     <row r="4259" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4259" s="2"/>
+      <c r="N4259" s="1"/>
     </row>
     <row r="4260" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4260" s="2"/>
@@ -8815,7 +10049,6 @@
     </row>
     <row r="4262" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4262" s="2"/>
-      <c r="N4262" s="1"/>
     </row>
     <row r="4263" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4263" s="2"/>
@@ -8823,6 +10056,7 @@
     </row>
     <row r="4264" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4264" s="2"/>
+      <c r="N4264" s="1"/>
     </row>
     <row r="4265" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4265" s="2"/>
@@ -8835,20 +10069,20 @@
     </row>
     <row r="4268" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4268" s="2"/>
-      <c r="N4268" s="1"/>
     </row>
     <row r="4269" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E4269" s="2"/>
+      <c r="N4269" s="1"/>
+    </row>
+    <row r="4270" spans="5:14" x14ac:dyDescent="0.45">
+      <c r="E4270" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="10">
+    <mergeCell ref="S3:T3"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="O3:P3"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="Q3:R3"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
